--- a/src/main/resources/rag/意图泛化语料.xlsx
+++ b/src/main/resources/rag/意图泛化语料.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="491">
   <si>
     <t>历史提问</t>
   </si>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>{"intent":"loan_application","parameters":{"amount":"5000","term":"6"}}</t>
+  </si>
+  <si>
+    <t>用户在提问中表明要借3500，因此提取用户意图为借款申请，金额为3500，提问中没有分期数和借款用途，分期数为空，借款用途为空</t>
+  </si>
+  <si>
+    <t>{"intent":"loan_application","parameters":{"amount":"3500"}}</t>
   </si>
   <si>
     <t>调整借款</t>
@@ -2160,10 +2166,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
@@ -2512,10 +2521,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F410"/>
+  <dimension ref="A1:F411"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="70.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="47.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="36.2222222222222" customWidth="1"/>
     <col min="3" max="3" width="173.888888888889" customWidth="1"/>
     <col min="4" max="4" width="10.7777777777778" customWidth="1"/>
@@ -2603,15 +2612,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5" spans="2:6">
+      <c r="B5" s="2">
+        <v>3500</v>
+      </c>
+      <c r="C5" t="s">
         <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
@@ -2620,7 +2626,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2628,10 +2634,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
         <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
@@ -2640,7 +2646,7 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2660,7 +2666,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2680,7 +2686,7 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2700,7 +2706,7 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2720,7 +2726,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2740,7 +2746,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2760,7 +2766,7 @@
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2780,7 +2786,7 @@
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2791,7 +2797,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
@@ -2800,7 +2806,7 @@
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2808,10 +2814,10 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
         <v>38</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
       </c>
       <c r="D15" t="s">
         <v>9</v>
@@ -2820,7 +2826,7 @@
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2831,7 +2837,7 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
@@ -2840,7 +2846,7 @@
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2848,10 +2854,10 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
         <v>41</v>
-      </c>
-      <c r="C17" t="s">
-        <v>42</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
@@ -2860,7 +2866,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2880,7 +2886,7 @@
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2900,7 +2906,7 @@
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2920,7 +2926,7 @@
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2940,7 +2946,7 @@
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2960,7 +2966,7 @@
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2980,7 +2986,7 @@
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3000,7 +3006,7 @@
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -3020,7 +3026,7 @@
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -3040,7 +3046,7 @@
         <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -3060,7 +3066,7 @@
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -3080,7 +3086,7 @@
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -3100,7 +3106,7 @@
         <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -3120,7 +3126,7 @@
         <v>10</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -3128,10 +3134,10 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
@@ -3140,7 +3146,7 @@
         <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -3148,10 +3154,10 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s">
         <v>9</v>
@@ -3160,7 +3166,7 @@
         <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -3180,7 +3186,7 @@
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -3200,7 +3206,7 @@
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -3220,7 +3226,7 @@
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -3240,7 +3246,7 @@
         <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -3260,7 +3266,7 @@
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -3268,10 +3274,10 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -3280,18 +3286,18 @@
         <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
@@ -3300,18 +3306,18 @@
         <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B40" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" t="s">
         <v>85</v>
-      </c>
-      <c r="B40" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" t="s">
-        <v>87</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
@@ -3320,15 +3326,18 @@
         <v>10</v>
       </c>
       <c r="F40" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>87</v>
+      </c>
+      <c r="B41" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="2" t="s">
+      <c r="C41" t="s">
         <v>89</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>
@@ -3337,15 +3346,15 @@
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="2:6">
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>90</v>
+      <c r="C42" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D42" t="s">
         <v>9</v>
@@ -3354,15 +3363,15 @@
         <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D43" t="s">
         <v>9</v>
@@ -3371,15 +3380,15 @@
         <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>90</v>
+      <c r="B44" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D44" t="s">
         <v>9</v>
@@ -3388,15 +3397,15 @@
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="2:6">
-      <c r="B45" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>90</v>
+      <c r="B45" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D45" t="s">
         <v>9</v>
@@ -3405,15 +3414,15 @@
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="2:6">
-      <c r="B46" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>90</v>
+      <c r="B46" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D46" t="s">
         <v>9</v>
@@ -3422,15 +3431,15 @@
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>90</v>
+      <c r="B47" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D47" t="s">
         <v>9</v>
@@ -3439,15 +3448,15 @@
         <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="2:6">
-      <c r="B48" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>90</v>
+      <c r="B48" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D48" t="s">
         <v>9</v>
@@ -3456,15 +3465,15 @@
         <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="2:6">
-      <c r="B49" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>90</v>
+      <c r="B49" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D49" t="s">
         <v>9</v>
@@ -3473,15 +3482,15 @@
         <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>90</v>
+      <c r="B50" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D50" t="s">
         <v>9</v>
@@ -3490,15 +3499,15 @@
         <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>90</v>
+      <c r="B51" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D51" t="s">
         <v>9</v>
@@ -3507,15 +3516,15 @@
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>90</v>
+      <c r="B52" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D52" t="s">
         <v>9</v>
@@ -3524,15 +3533,15 @@
         <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C53" s="2" t="s">
+      <c r="B53" s="3" t="s">
         <v>103</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="D53" t="s">
         <v>9</v>
@@ -3541,15 +3550,15 @@
         <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>103</v>
+      <c r="C54" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="D54" t="s">
         <v>9</v>
@@ -3558,15 +3567,15 @@
         <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="D55" t="s">
         <v>9</v>
@@ -3575,4899 +3584,4916 @@
         <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="2:6">
-      <c r="B56" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="B56" s="3" t="s">
         <v>107</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="D56" t="s">
         <v>9</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6">
+      <c r="B57" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F56" t="s">
+      <c r="C57" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D57" t="s">
         <v>9</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>108</v>
+      <c r="E57" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D58" t="s">
         <v>9</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>108</v>
+      <c r="E58" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F58" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6">
-      <c r="B59" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D59" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>108</v>
+      <c r="E59" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F59" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6">
+      <c r="B60" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6">
-      <c r="B60" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D60" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>108</v>
+      <c r="E60" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F60" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D61" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>108</v>
+      <c r="E61" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F61" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6">
-      <c r="B62" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D62" t="s">
         <v>9</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>108</v>
+      <c r="E62" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F62" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6">
+      <c r="B63" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D63" t="s">
         <v>9</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>108</v>
+      <c r="E63" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F63" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D64" t="s">
         <v>9</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>108</v>
+      <c r="E64" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F64" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
+      <c r="B65" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6">
-      <c r="B65" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D65" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>108</v>
+      <c r="E65" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F65" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
+      <c r="B66" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6">
-      <c r="B66" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D66" t="s">
         <v>9</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>108</v>
+      <c r="E66" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F66" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6">
+      <c r="B67" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6">
-      <c r="B67" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D67" t="s">
         <v>9</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>108</v>
+      <c r="E67" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F67" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6">
+      <c r="B68" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6">
-      <c r="B68" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D68" t="s">
         <v>9</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>108</v>
+      <c r="E68" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F68" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6">
+      <c r="B69" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6">
-      <c r="B69" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D69" t="s">
         <v>9</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>108</v>
+      <c r="E69" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F69" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6">
+      <c r="B70" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="70" spans="2:6">
-      <c r="B70" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>108</v>
+      <c r="E70" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F70" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
+      <c r="B71" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6">
-      <c r="B71" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D71" t="s">
         <v>9</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>108</v>
+      <c r="E71" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="F71" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6">
+      <c r="B72" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="72" spans="2:6">
-      <c r="B72" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E72" s="2" t="s">
+      <c r="D72" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F72" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6">
+      <c r="B73" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="73" spans="2:6">
-      <c r="B73" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>128</v>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="74" spans="2:6">
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F74" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>128</v>
-      </c>
     </row>
     <row r="75" spans="2:6">
-      <c r="B75" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>128</v>
+      <c r="B75" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F76" s="2" t="s">
+      <c r="B76" s="3" t="s">
         <v>133</v>
       </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="77" spans="2:6">
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>133</v>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="78" spans="2:6">
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F78" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="79" spans="2:6">
-      <c r="B79" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>133</v>
+      <c r="B79" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="80" spans="2:6">
-      <c r="B80" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>133</v>
+      <c r="B80" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>133</v>
+      <c r="B81" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="82" spans="2:6">
-      <c r="B82" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>133</v>
+      <c r="B82" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="83" spans="2:6">
-      <c r="B83" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>133</v>
+      <c r="B83" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="84" spans="2:6">
-      <c r="B84" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>133</v>
+      <c r="B84" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="85" spans="2:6">
-      <c r="B85" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>133</v>
+      <c r="B85" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="86" spans="2:6">
-      <c r="B86" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>133</v>
+      <c r="B86" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="87" spans="2:6">
-      <c r="B87" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>133</v>
+      <c r="B87" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="88" spans="2:6">
-      <c r="B88" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F88" s="2" t="s">
+      <c r="B88" s="3" t="s">
         <v>146</v>
       </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>146</v>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F90" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>146</v>
-      </c>
     </row>
     <row r="91" spans="2:6">
-      <c r="B91" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>146</v>
+      <c r="B91" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="92" spans="2:6">
-      <c r="B92" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>146</v>
+      <c r="B92" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="93" spans="2:6">
-      <c r="B93" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>146</v>
+      <c r="B93" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="94" spans="2:6">
-      <c r="B94" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>146</v>
+      <c r="B94" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="95" spans="2:6">
-      <c r="B95" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>146</v>
+      <c r="B95" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="96" spans="2:6">
-      <c r="B96" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F96" s="2" t="s">
+      <c r="B96" s="3" t="s">
         <v>155</v>
       </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>155</v>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F98" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>155</v>
-      </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>155</v>
+      <c r="B99" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>155</v>
+      <c r="B100" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>155</v>
+      <c r="B101" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="102" spans="2:6">
-      <c r="B102" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>155</v>
+      <c r="B102" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="103" spans="2:6">
-      <c r="B103" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>155</v>
+      <c r="B103" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="104" spans="2:6">
-      <c r="B104" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F104" s="2" t="s">
+      <c r="B104" s="3" t="s">
         <v>164</v>
       </c>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="105" spans="2:6">
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>164</v>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="106" spans="2:6">
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F106" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>164</v>
-      </c>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>164</v>
+      <c r="B107" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F108" s="2" t="s">
+      <c r="B108" s="3" t="s">
         <v>169</v>
       </c>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="109" spans="2:6">
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>169</v>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="110" spans="2:6">
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F110" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>169</v>
-      </c>
     </row>
     <row r="111" spans="2:6">
-      <c r="B111" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>169</v>
+      <c r="B111" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="112" spans="2:6">
-      <c r="B112" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>169</v>
+      <c r="B112" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="113" spans="2:6">
-      <c r="B113" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>169</v>
+      <c r="B113" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="114" spans="2:6">
-      <c r="B114" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>169</v>
+      <c r="B114" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="115" spans="2:6">
-      <c r="B115" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>169</v>
+      <c r="B115" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="116" spans="2:6">
-      <c r="B116" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>169</v>
+      <c r="B116" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="117" spans="2:6">
-      <c r="B117" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>169</v>
+      <c r="B117" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="118" spans="2:6">
-      <c r="B118" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>169</v>
+      <c r="B118" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="119" spans="2:6">
-      <c r="B119" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>169</v>
+      <c r="B119" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="120" spans="2:6">
-      <c r="B120" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F120" s="2" t="s">
+      <c r="B120" s="3" t="s">
         <v>182</v>
       </c>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="121" spans="2:6">
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>182</v>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="122" spans="2:6">
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F122" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>182</v>
-      </c>
     </row>
     <row r="123" spans="2:6">
-      <c r="B123" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>182</v>
+      <c r="B123" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F124" s="2" t="s">
+      <c r="B124" s="3" t="s">
         <v>187</v>
       </c>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="125" spans="2:6">
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C125" s="2"/>
-      <c r="D125" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>182</v>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="126" spans="2:6">
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6">
+      <c r="B127" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="128" spans="2:6">
+      <c r="B128" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="129" spans="2:6">
+      <c r="B129" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F129" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C126" s="2"/>
-      <c r="D126" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="127" spans="2:6">
-      <c r="B127" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="128" spans="2:6">
-      <c r="B128" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="129" spans="2:6">
-      <c r="B129" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>182</v>
-      </c>
     </row>
     <row r="130" spans="2:6">
-      <c r="B130" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>182</v>
+      <c r="B130" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="131" spans="2:6">
-      <c r="B131" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>182</v>
+      <c r="B131" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="132" spans="2:6">
-      <c r="B132" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F132" s="2" t="s">
+      <c r="B132" s="3" t="s">
         <v>196</v>
       </c>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="133" spans="2:6">
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>196</v>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="134" spans="2:6">
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F134" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C134" s="2"/>
-      <c r="D134" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>196</v>
-      </c>
     </row>
     <row r="135" spans="2:6">
-      <c r="B135" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>196</v>
+      <c r="B135" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="136" spans="2:6">
-      <c r="B136" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>196</v>
+      <c r="B136" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="137" spans="2:6">
-      <c r="B137" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>196</v>
+      <c r="B137" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="138" spans="2:6">
-      <c r="B138" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>196</v>
+      <c r="B138" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="139" spans="2:6">
-      <c r="B139" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>196</v>
+      <c r="B139" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="140" spans="2:6">
-      <c r="B140" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F140" s="2" t="s">
+      <c r="B140" s="3" t="s">
         <v>205</v>
       </c>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="141" spans="2:6">
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>205</v>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="142" spans="2:6">
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F142" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>205</v>
-      </c>
     </row>
     <row r="143" spans="2:6">
-      <c r="B143" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>205</v>
+      <c r="B143" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="144" spans="2:6">
-      <c r="B144" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C144" s="2"/>
-      <c r="D144" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>205</v>
+      <c r="B144" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="145" spans="2:6">
-      <c r="B145" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>205</v>
+      <c r="B145" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="146" spans="2:6">
-      <c r="B146" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>205</v>
+      <c r="B146" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="147" spans="2:6">
-      <c r="B147" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>205</v>
+      <c r="B147" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="148" spans="2:6">
-      <c r="B148" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F148" s="2" t="s">
+      <c r="B148" s="3" t="s">
         <v>214</v>
       </c>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="149" spans="2:6">
-      <c r="B149" s="2" t="s">
+      <c r="B149" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C149" s="2"/>
-      <c r="D149" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F149" s="2" t="s">
-        <v>214</v>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="150" spans="2:6">
-      <c r="B150" s="2" t="s">
+      <c r="B150" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F150" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C150" s="2"/>
-      <c r="D150" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>214</v>
-      </c>
     </row>
     <row r="151" spans="2:6">
-      <c r="B151" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>214</v>
+      <c r="B151" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="152" spans="2:6">
-      <c r="B152" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C152" s="2"/>
-      <c r="D152" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>214</v>
+      <c r="B152" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="153" spans="2:6">
-      <c r="B153" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>214</v>
+      <c r="B153" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="154" spans="2:6">
-      <c r="B154" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C154" s="2"/>
-      <c r="D154" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>214</v>
+      <c r="B154" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="155" spans="2:6">
-      <c r="B155" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C155" s="2"/>
-      <c r="D155" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E155" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>214</v>
+      <c r="B155" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="156" spans="2:6">
-      <c r="B156" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C156" s="2"/>
-      <c r="D156" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F156" s="2" t="s">
+      <c r="B156" s="3" t="s">
         <v>223</v>
       </c>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="157" spans="2:6">
-      <c r="B157" s="2" t="s">
+      <c r="B157" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C157" s="2"/>
-      <c r="D157" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E157" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F157" s="2" t="s">
-        <v>223</v>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="158" spans="2:6">
-      <c r="B158" s="2" t="s">
+      <c r="B158" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F158" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C158" s="2"/>
-      <c r="D158" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>223</v>
-      </c>
     </row>
     <row r="159" spans="2:6">
-      <c r="B159" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C159" s="2"/>
-      <c r="D159" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F159" s="2" t="s">
-        <v>223</v>
+      <c r="B159" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="160" spans="2:6">
-      <c r="B160" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C160" s="2"/>
-      <c r="D160" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F160" s="2" t="s">
+      <c r="B160" s="3" t="s">
         <v>228</v>
       </c>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="2" t="s">
+      <c r="B161" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C161" s="2"/>
-      <c r="D161" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>228</v>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="2" t="s">
+      <c r="B162" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F162" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C162" s="2"/>
-      <c r="D162" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F162" s="2" t="s">
-        <v>228</v>
-      </c>
     </row>
     <row r="163" spans="2:6">
-      <c r="B163" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C163" s="2"/>
-      <c r="D163" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F163" s="2" t="s">
-        <v>228</v>
+      <c r="B163" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="164" spans="2:6">
-      <c r="B164" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C164" s="2"/>
-      <c r="D164" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F164" s="2" t="s">
+      <c r="B164" s="3" t="s">
         <v>233</v>
       </c>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="165" spans="2:6">
-      <c r="B165" s="2" t="s">
+      <c r="B165" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C165" s="2"/>
-      <c r="D165" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>233</v>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="166" spans="2:6">
-      <c r="B166" s="2" t="s">
+      <c r="B166" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F166" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C166" s="2"/>
-      <c r="D166" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F166" s="2" t="s">
-        <v>233</v>
-      </c>
     </row>
     <row r="167" spans="2:6">
-      <c r="B167" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C167" s="2"/>
-      <c r="D167" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F167" s="2" t="s">
-        <v>233</v>
+      <c r="B167" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="168" spans="2:6">
-      <c r="B168" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C168" s="2"/>
-      <c r="D168" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F168" s="2" t="s">
+      <c r="B168" s="3" t="s">
         <v>238</v>
       </c>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="169" spans="2:6">
-      <c r="B169" s="2" t="s">
+      <c r="B169" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C169" s="2"/>
-      <c r="D169" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F169" s="2" t="s">
-        <v>238</v>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="170" spans="2:6">
-      <c r="B170" s="2" t="s">
+      <c r="B170" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F170" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C170" s="2"/>
-      <c r="D170" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F170" s="2" t="s">
-        <v>238</v>
-      </c>
     </row>
     <row r="171" spans="2:6">
-      <c r="B171" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C171" s="2"/>
-      <c r="D171" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F171" s="2" t="s">
-        <v>238</v>
+      <c r="B171" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="172" spans="2:6">
-      <c r="B172" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C172" s="2"/>
-      <c r="D172" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E172" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F172" s="2" t="s">
+      <c r="B172" s="3" t="s">
         <v>243</v>
       </c>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="173" spans="2:6">
-      <c r="B173" s="2" t="s">
+      <c r="B173" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C173" s="2"/>
-      <c r="D173" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F173" s="2" t="s">
-        <v>243</v>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="174" spans="2:6">
-      <c r="B174" s="2" t="s">
+      <c r="B174" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F174" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C174" s="2"/>
-      <c r="D174" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F174" s="2" t="s">
-        <v>243</v>
-      </c>
     </row>
     <row r="175" spans="2:6">
-      <c r="B175" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C175" s="2"/>
-      <c r="D175" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>243</v>
+      <c r="B175" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="176" spans="2:6">
-      <c r="B176" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C176" s="2"/>
-      <c r="D176" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F176" s="2" t="s">
+      <c r="B176" s="3" t="s">
         <v>248</v>
       </c>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="2" t="s">
+      <c r="B177" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C177" s="2"/>
-      <c r="D177" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F177" s="2" t="s">
-        <v>248</v>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="178" spans="2:6">
-      <c r="B178" s="2" t="s">
+      <c r="B178" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F178" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C178" s="2"/>
-      <c r="D178" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F178" s="2" t="s">
-        <v>248</v>
-      </c>
     </row>
     <row r="179" spans="2:6">
-      <c r="B179" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C179" s="2"/>
-      <c r="D179" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F179" s="2" t="s">
-        <v>248</v>
+      <c r="B179" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="180" spans="2:6">
-      <c r="B180" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C180" s="2"/>
-      <c r="D180" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E180" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F180" s="2" t="s">
-        <v>182</v>
+      <c r="B180" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="181" spans="2:6">
-      <c r="B181" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C181" s="2"/>
-      <c r="D181" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F181" s="2" t="s">
-        <v>182</v>
+      <c r="B181" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="182" spans="2:6">
-      <c r="B182" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C182" s="2"/>
-      <c r="D182" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F182" s="2" t="s">
-        <v>182</v>
+      <c r="B182" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="183" spans="2:6">
-      <c r="B183" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C183" s="2"/>
-      <c r="D183" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F183" s="2" t="s">
-        <v>182</v>
+      <c r="B183" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="184" spans="2:6">
-      <c r="B184" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C184" s="2"/>
-      <c r="D184" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E184" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F184" s="2" t="s">
+      <c r="B184" s="3" t="s">
         <v>257</v>
       </c>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="185" spans="2:6">
-      <c r="B185" s="2" t="s">
+      <c r="B185" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C185" s="2"/>
-      <c r="D185" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F185" s="2" t="s">
-        <v>257</v>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="186" spans="2:6">
-      <c r="B186" s="2" t="s">
+      <c r="B186" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F186" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C186" s="2"/>
-      <c r="D186" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F186" s="2" t="s">
-        <v>257</v>
-      </c>
     </row>
     <row r="187" spans="2:6">
-      <c r="B187" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C187" s="2"/>
-      <c r="D187" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F187" s="2" t="s">
-        <v>257</v>
+      <c r="B187" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="188" spans="2:6">
-      <c r="B188" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C188" s="2"/>
-      <c r="D188" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F188" s="2" t="s">
-        <v>257</v>
+      <c r="B188" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="189" spans="2:6">
-      <c r="B189" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C189" s="2"/>
-      <c r="D189" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F189" s="2" t="s">
-        <v>257</v>
+      <c r="B189" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="190" spans="2:6">
-      <c r="B190" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C190" s="2"/>
-      <c r="D190" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E190" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F190" s="2" t="s">
-        <v>257</v>
+      <c r="B190" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="191" spans="2:6">
-      <c r="B191" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C191" s="2"/>
-      <c r="D191" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>257</v>
+      <c r="B191" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="192" spans="2:6">
-      <c r="B192" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C192" s="2"/>
-      <c r="D192" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F192" s="2" t="s">
+      <c r="B192" s="3" t="s">
         <v>266</v>
       </c>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="193" spans="2:6">
-      <c r="B193" s="2" t="s">
+      <c r="B193" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="C193" s="2"/>
-      <c r="D193" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F193" s="2" t="s">
-        <v>266</v>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="194" spans="2:6">
-      <c r="B194" s="2" t="s">
+      <c r="B194" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F194" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C194" s="2"/>
-      <c r="D194" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>266</v>
-      </c>
     </row>
     <row r="195" spans="2:6">
-      <c r="B195" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C195" s="2"/>
-      <c r="D195" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F195" s="2" t="s">
-        <v>266</v>
+      <c r="B195" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="196" spans="2:6">
-      <c r="B196" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C196" s="2"/>
-      <c r="D196" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F196" s="2" t="s">
+      <c r="B196" s="3" t="s">
         <v>271</v>
       </c>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="197" spans="2:6">
-      <c r="B197" s="2" t="s">
+      <c r="B197" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C197" s="2"/>
-      <c r="D197" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>271</v>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="198" spans="2:6">
-      <c r="B198" s="2" t="s">
+      <c r="B198" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F198" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C198" s="2"/>
-      <c r="D198" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>271</v>
-      </c>
     </row>
     <row r="199" spans="2:6">
-      <c r="B199" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C199" s="2"/>
-      <c r="D199" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>271</v>
+      <c r="B199" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="200" spans="2:6">
-      <c r="B200" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C200" s="2"/>
-      <c r="D200" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F200" s="2" t="s">
+      <c r="B200" s="3" t="s">
         <v>276</v>
       </c>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="201" spans="2:6">
-      <c r="B201" s="2" t="s">
+      <c r="B201" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C201" s="2"/>
-      <c r="D201" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>276</v>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="202" spans="2:6">
-      <c r="B202" s="2" t="s">
+      <c r="B202" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F202" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C202" s="2"/>
-      <c r="D202" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>276</v>
-      </c>
     </row>
     <row r="203" spans="2:6">
-      <c r="B203" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C203" s="2"/>
-      <c r="D203" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>276</v>
+      <c r="B203" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C203" s="3"/>
+      <c r="D203" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="204" spans="2:6">
-      <c r="B204" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C204" s="2"/>
-      <c r="D204" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F204" s="2" t="s">
+      <c r="B204" s="3" t="s">
         <v>281</v>
       </c>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="205" spans="2:6">
-      <c r="B205" s="2" t="s">
+      <c r="B205" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>281</v>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="206" spans="2:6">
-      <c r="B206" s="2" t="s">
+      <c r="B206" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C206" s="3"/>
+      <c r="D206" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F206" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C206" s="2"/>
-      <c r="D206" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>281</v>
-      </c>
     </row>
     <row r="207" spans="2:6">
-      <c r="B207" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C207" s="2"/>
-      <c r="D207" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>281</v>
+      <c r="B207" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="208" spans="2:6">
-      <c r="B208" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C208" s="2"/>
-      <c r="D208" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>182</v>
+      <c r="B208" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="209" spans="2:6">
-      <c r="B209" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C209" s="2"/>
-      <c r="D209" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>182</v>
+      <c r="B209" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="210" spans="2:6">
-      <c r="B210" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C210" s="2"/>
-      <c r="D210" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>182</v>
+      <c r="B210" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="211" spans="2:6">
-      <c r="B211" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C211" s="2"/>
-      <c r="D211" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>182</v>
+      <c r="B211" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="212" spans="2:6">
-      <c r="B212" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C212" s="2"/>
-      <c r="D212" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>182</v>
+      <c r="B212" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C212" s="3"/>
+      <c r="D212" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="213" spans="2:6">
-      <c r="B213" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C213" s="2"/>
-      <c r="D213" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>182</v>
+      <c r="B213" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C213" s="3"/>
+      <c r="D213" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="214" spans="2:6">
-      <c r="B214" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C214" s="2"/>
-      <c r="D214" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>182</v>
+      <c r="B214" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="215" spans="2:6">
-      <c r="B215" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C215" s="2"/>
-      <c r="D215" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>182</v>
+      <c r="B215" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="216" spans="2:6">
-      <c r="B216" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C216" s="2"/>
-      <c r="D216" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F216" s="2" t="s">
+      <c r="B216" s="3" t="s">
         <v>294</v>
       </c>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="217" spans="2:6">
-      <c r="B217" s="2" t="s">
+      <c r="B217" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C217" s="2"/>
-      <c r="D217" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>294</v>
+      <c r="C217" s="3"/>
+      <c r="D217" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="218" spans="2:6">
-      <c r="B218" s="2" t="s">
+      <c r="B218" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C218" s="3"/>
+      <c r="D218" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F218" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C218" s="2"/>
-      <c r="D218" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>294</v>
-      </c>
     </row>
     <row r="219" spans="2:6">
-      <c r="B219" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C219" s="2"/>
-      <c r="D219" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>294</v>
+      <c r="B219" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C219" s="3"/>
+      <c r="D219" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="220" spans="2:6">
-      <c r="B220" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C220" s="2"/>
-      <c r="D220" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F220" s="2" t="s">
+      <c r="B220" s="3" t="s">
         <v>299</v>
       </c>
+      <c r="C220" s="3"/>
+      <c r="D220" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E220" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="221" spans="2:6">
-      <c r="B221" s="2" t="s">
+      <c r="B221" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C221" s="2"/>
-      <c r="D221" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>299</v>
+      <c r="C221" s="3"/>
+      <c r="D221" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="222" spans="2:6">
-      <c r="B222" s="2" t="s">
+      <c r="B222" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C222" s="3"/>
+      <c r="D222" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F222" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="C222" s="2"/>
-      <c r="D222" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>299</v>
-      </c>
     </row>
     <row r="223" spans="2:6">
-      <c r="B223" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C223" s="2"/>
-      <c r="D223" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>299</v>
+      <c r="B223" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C223" s="3"/>
+      <c r="D223" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="224" spans="2:6">
-      <c r="B224" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C224" s="2"/>
-      <c r="D224" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F224" s="2" t="s">
+      <c r="B224" s="3" t="s">
         <v>304</v>
       </c>
+      <c r="C224" s="3"/>
+      <c r="D224" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="225" spans="2:6">
-      <c r="B225" s="2" t="s">
+      <c r="B225" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="C225" s="2"/>
-      <c r="D225" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>304</v>
+      <c r="C225" s="3"/>
+      <c r="D225" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="226" spans="2:6">
-      <c r="B226" s="2" t="s">
+      <c r="B226" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C226" s="3"/>
+      <c r="D226" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F226" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C226" s="2"/>
-      <c r="D226" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="227" spans="2:6">
-      <c r="B227" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="C227" s="2"/>
-      <c r="D227" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>304</v>
+      <c r="B227" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C227" s="3"/>
+      <c r="D227" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="228" spans="2:6">
-      <c r="B228" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C228" s="2"/>
-      <c r="D228" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>182</v>
+      <c r="B228" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C228" s="3"/>
+      <c r="D228" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="229" spans="2:6">
-      <c r="B229" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C229" s="2"/>
-      <c r="D229" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E229" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>182</v>
+      <c r="B229" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C229" s="3"/>
+      <c r="D229" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="230" spans="2:6">
-      <c r="B230" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C230" s="2"/>
-      <c r="D230" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>182</v>
+      <c r="B230" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C230" s="3"/>
+      <c r="D230" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="231" spans="2:6">
-      <c r="B231" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C231" s="2"/>
-      <c r="D231" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>182</v>
+      <c r="B231" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C231" s="3"/>
+      <c r="D231" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="232" spans="2:6">
-      <c r="B232" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C232" s="2"/>
-      <c r="D232" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F232" s="2" t="s">
+      <c r="B232" s="3" t="s">
         <v>313</v>
       </c>
+      <c r="C232" s="3"/>
+      <c r="D232" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E232" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="233" spans="2:6">
-      <c r="B233" s="2" t="s">
+      <c r="B233" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C233" s="2"/>
-      <c r="D233" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>313</v>
+      <c r="C233" s="3"/>
+      <c r="D233" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="234" spans="2:6">
-      <c r="B234" s="2" t="s">
+      <c r="B234" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C234" s="3"/>
+      <c r="D234" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E234" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F234" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="C234" s="2"/>
-      <c r="D234" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>313</v>
-      </c>
     </row>
     <row r="235" spans="2:6">
-      <c r="B235" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C235" s="2"/>
-      <c r="D235" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>313</v>
+      <c r="B235" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C235" s="3"/>
+      <c r="D235" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="236" spans="2:6">
-      <c r="B236" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C236" s="2"/>
-      <c r="D236" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F236" s="2" t="s">
+      <c r="B236" s="3" t="s">
         <v>318</v>
       </c>
+      <c r="C236" s="3"/>
+      <c r="D236" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="237" spans="2:6">
-      <c r="B237" s="2" t="s">
+      <c r="B237" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C237" s="2"/>
-      <c r="D237" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>318</v>
+      <c r="C237" s="3"/>
+      <c r="D237" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="238" spans="2:6">
-      <c r="B238" s="2" t="s">
+      <c r="B238" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C238" s="3"/>
+      <c r="D238" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F238" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="C238" s="2"/>
-      <c r="D238" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>318</v>
-      </c>
     </row>
     <row r="239" spans="2:6">
-      <c r="B239" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C239" s="2"/>
-      <c r="D239" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>318</v>
+      <c r="B239" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C239" s="3"/>
+      <c r="D239" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="240" spans="2:6">
-      <c r="B240" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="C240" s="2"/>
-      <c r="D240" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F240" s="2" t="s">
+      <c r="B240" s="3" t="s">
         <v>323</v>
       </c>
+      <c r="C240" s="3"/>
+      <c r="D240" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="241" spans="2:6">
-      <c r="B241" s="2" t="s">
+      <c r="B241" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="C241" s="2"/>
-      <c r="D241" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>323</v>
+      <c r="C241" s="3"/>
+      <c r="D241" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="242" spans="2:6">
-      <c r="B242" s="2" t="s">
+      <c r="B242" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C242" s="3"/>
+      <c r="D242" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F242" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="C242" s="2"/>
-      <c r="D242" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>323</v>
-      </c>
     </row>
     <row r="243" spans="2:6">
-      <c r="B243" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C243" s="2"/>
-      <c r="D243" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>323</v>
+      <c r="B243" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C243" s="3"/>
+      <c r="D243" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="244" spans="2:6">
-      <c r="B244" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="C244" s="2"/>
-      <c r="D244" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F244" s="2" t="s">
+      <c r="B244" s="3" t="s">
         <v>328</v>
       </c>
+      <c r="C244" s="3"/>
+      <c r="D244" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="245" spans="2:6">
-      <c r="B245" s="2" t="s">
+      <c r="B245" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="C245" s="2"/>
-      <c r="D245" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>328</v>
+      <c r="C245" s="3"/>
+      <c r="D245" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="246" spans="2:6">
-      <c r="B246" s="2" t="s">
+      <c r="B246" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C246" s="3"/>
+      <c r="D246" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F246" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C246" s="2"/>
-      <c r="D246" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>328</v>
-      </c>
     </row>
     <row r="247" spans="2:6">
-      <c r="B247" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C247" s="2"/>
-      <c r="D247" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>328</v>
+      <c r="B247" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C247" s="3"/>
+      <c r="D247" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="248" spans="2:6">
-      <c r="B248" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C248" s="2"/>
-      <c r="D248" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F248" s="2" t="s">
+      <c r="B248" s="3" t="s">
         <v>333</v>
       </c>
+      <c r="C248" s="3"/>
+      <c r="D248" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="249" spans="2:6">
-      <c r="B249" s="2" t="s">
+      <c r="B249" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C249" s="2"/>
-      <c r="D249" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F249" s="2" t="s">
-        <v>333</v>
+      <c r="C249" s="3"/>
+      <c r="D249" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="250" spans="2:6">
-      <c r="B250" s="2" t="s">
+      <c r="B250" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C250" s="3"/>
+      <c r="D250" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F250" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="C250" s="2"/>
-      <c r="D250" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>333</v>
-      </c>
     </row>
     <row r="251" spans="2:6">
-      <c r="B251" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="C251" s="2"/>
-      <c r="D251" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>333</v>
+      <c r="B251" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C251" s="3"/>
+      <c r="D251" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="252" spans="2:6">
-      <c r="B252" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C252" s="2"/>
-      <c r="D252" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F252" s="2" t="s">
+      <c r="B252" s="3" t="s">
         <v>338</v>
       </c>
+      <c r="C252" s="3"/>
+      <c r="D252" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="253" spans="2:6">
-      <c r="B253" s="2" t="s">
+      <c r="B253" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="C253" s="2"/>
-      <c r="D253" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>338</v>
+      <c r="C253" s="3"/>
+      <c r="D253" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="254" spans="2:6">
-      <c r="B254" s="2" t="s">
+      <c r="B254" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C254" s="3"/>
+      <c r="D254" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F254" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="C254" s="2"/>
-      <c r="D254" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>338</v>
-      </c>
     </row>
     <row r="255" spans="2:6">
-      <c r="B255" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C255" s="2"/>
-      <c r="D255" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>338</v>
+      <c r="B255" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C255" s="3"/>
+      <c r="D255" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="256" spans="2:6">
-      <c r="B256" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C256" s="2"/>
-      <c r="D256" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F256" s="2" t="s">
+      <c r="B256" s="3" t="s">
         <v>343</v>
       </c>
+      <c r="C256" s="3"/>
+      <c r="D256" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E256" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="257" spans="2:6">
-      <c r="B257" s="2" t="s">
+      <c r="B257" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="C257" s="2"/>
-      <c r="D257" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>343</v>
+      <c r="C257" s="3"/>
+      <c r="D257" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="258" spans="2:6">
-      <c r="B258" s="2" t="s">
+      <c r="B258" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C258" s="3"/>
+      <c r="D258" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F258" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C258" s="2"/>
-      <c r="D258" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>343</v>
-      </c>
     </row>
     <row r="259" spans="2:6">
-      <c r="B259" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C259" s="2"/>
-      <c r="D259" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F259" s="2" t="s">
-        <v>343</v>
+      <c r="B259" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C259" s="3"/>
+      <c r="D259" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="260" spans="2:6">
-      <c r="B260" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="C260" s="2"/>
-      <c r="D260" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F260" s="2" t="s">
+      <c r="B260" s="3" t="s">
         <v>348</v>
       </c>
+      <c r="C260" s="3"/>
+      <c r="D260" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="261" spans="2:6">
-      <c r="B261" s="2" t="s">
+      <c r="B261" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="C261" s="2"/>
-      <c r="D261" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E261" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F261" s="2" t="s">
-        <v>348</v>
+      <c r="C261" s="3"/>
+      <c r="D261" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="262" spans="2:6">
-      <c r="B262" s="2" t="s">
+      <c r="B262" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C262" s="3"/>
+      <c r="D262" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F262" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="C262" s="2"/>
-      <c r="D262" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F262" s="2" t="s">
-        <v>348</v>
-      </c>
     </row>
     <row r="263" spans="2:6">
-      <c r="B263" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C263" s="2"/>
-      <c r="D263" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E263" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F263" s="2" t="s">
-        <v>348</v>
+      <c r="B263" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C263" s="3"/>
+      <c r="D263" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="264" spans="2:6">
-      <c r="B264" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C264" s="2"/>
-      <c r="D264" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E264" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F264" s="2" t="s">
+      <c r="B264" s="3" t="s">
         <v>353</v>
       </c>
+      <c r="C264" s="3"/>
+      <c r="D264" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="265" spans="2:6">
-      <c r="B265" s="2" t="s">
+      <c r="B265" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="C265" s="2"/>
-      <c r="D265" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E265" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F265" s="2" t="s">
-        <v>353</v>
+      <c r="C265" s="3"/>
+      <c r="D265" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="266" spans="2:6">
-      <c r="B266" s="2" t="s">
+      <c r="B266" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C266" s="3"/>
+      <c r="D266" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E266" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F266" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="C266" s="2"/>
-      <c r="D266" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E266" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F266" s="2" t="s">
-        <v>353</v>
-      </c>
     </row>
     <row r="267" spans="2:6">
-      <c r="B267" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C267" s="2"/>
-      <c r="D267" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F267" s="2" t="s">
-        <v>353</v>
+      <c r="B267" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C267" s="3"/>
+      <c r="D267" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="268" spans="2:6">
-      <c r="B268" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C268" s="2"/>
-      <c r="D268" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E268" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F268" s="2" t="s">
+      <c r="B268" s="3" t="s">
         <v>358</v>
       </c>
+      <c r="C268" s="3"/>
+      <c r="D268" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E268" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="269" spans="2:6">
-      <c r="B269" s="2" t="s">
+      <c r="B269" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="C269" s="2"/>
-      <c r="D269" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>358</v>
+      <c r="C269" s="3"/>
+      <c r="D269" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="270" spans="2:6">
-      <c r="B270" s="2" t="s">
+      <c r="B270" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C270" s="3"/>
+      <c r="D270" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F270" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="C270" s="2"/>
-      <c r="D270" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F270" s="2" t="s">
-        <v>358</v>
-      </c>
     </row>
     <row r="271" spans="2:6">
-      <c r="B271" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C271" s="2"/>
-      <c r="D271" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E271" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F271" s="2" t="s">
-        <v>358</v>
+      <c r="B271" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C271" s="3"/>
+      <c r="D271" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="272" spans="2:6">
-      <c r="B272" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="C272" s="2"/>
-      <c r="D272" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E272" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F272" s="2" t="s">
+      <c r="B272" s="3" t="s">
         <v>363</v>
       </c>
+      <c r="C272" s="3"/>
+      <c r="D272" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E272" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="273" spans="2:6">
-      <c r="B273" s="2" t="s">
+      <c r="B273" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="C273" s="2"/>
-      <c r="D273" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>363</v>
+      <c r="C273" s="3"/>
+      <c r="D273" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F273" s="3" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="274" spans="2:6">
-      <c r="B274" s="2" t="s">
+      <c r="B274" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C274" s="3"/>
+      <c r="D274" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E274" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F274" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C274" s="2"/>
-      <c r="D274" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F274" s="2" t="s">
-        <v>363</v>
-      </c>
     </row>
     <row r="275" spans="2:6">
-      <c r="B275" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C275" s="2"/>
-      <c r="D275" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>363</v>
+      <c r="B275" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C275" s="3"/>
+      <c r="D275" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E275" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="276" spans="2:6">
-      <c r="B276" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C276" s="2"/>
-      <c r="D276" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E276" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F276" s="2" t="s">
+      <c r="B276" s="3" t="s">
         <v>368</v>
       </c>
+      <c r="C276" s="3"/>
+      <c r="D276" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>365</v>
+      </c>
     </row>
     <row r="277" spans="2:6">
-      <c r="B277" s="2" t="s">
+      <c r="B277" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="C277" s="2"/>
-      <c r="D277" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E277" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F277" s="2" t="s">
-        <v>368</v>
+      <c r="C277" s="3"/>
+      <c r="D277" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E277" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="278" spans="2:6">
-      <c r="B278" s="2" t="s">
+      <c r="B278" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C278" s="3"/>
+      <c r="D278" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E278" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F278" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C278" s="2"/>
-      <c r="D278" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>368</v>
-      </c>
     </row>
     <row r="279" spans="2:6">
-      <c r="B279" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C279" s="2"/>
-      <c r="D279" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E279" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F279" s="2" t="s">
-        <v>368</v>
+      <c r="B279" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C279" s="3"/>
+      <c r="D279" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="280" spans="2:6">
-      <c r="B280" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C280" s="2"/>
-      <c r="D280" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E280" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F280" s="2" t="s">
+      <c r="B280" s="3" t="s">
         <v>373</v>
       </c>
+      <c r="C280" s="3"/>
+      <c r="D280" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E280" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>370</v>
+      </c>
     </row>
     <row r="281" spans="2:6">
-      <c r="B281" s="2" t="s">
+      <c r="B281" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="C281" s="2"/>
-      <c r="D281" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>373</v>
+      <c r="C281" s="3"/>
+      <c r="D281" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E281" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F281" s="3" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="282" spans="2:6">
-      <c r="B282" s="2" t="s">
+      <c r="B282" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C282" s="3"/>
+      <c r="D282" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F282" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="C282" s="2"/>
-      <c r="D282" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F282" s="2" t="s">
-        <v>373</v>
-      </c>
     </row>
     <row r="283" spans="2:6">
-      <c r="B283" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="C283" s="2"/>
-      <c r="D283" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E283" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F283" s="2" t="s">
-        <v>373</v>
+      <c r="B283" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C283" s="3"/>
+      <c r="D283" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="284" spans="2:6">
-      <c r="B284" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="C284" s="2"/>
-      <c r="D284" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E284" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F284" s="2" t="s">
+      <c r="B284" s="3" t="s">
         <v>378</v>
       </c>
+      <c r="C284" s="3"/>
+      <c r="D284" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E284" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="285" spans="2:6">
-      <c r="B285" s="2" t="s">
+      <c r="B285" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="C285" s="2"/>
-      <c r="D285" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E285" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F285" s="2" t="s">
-        <v>378</v>
+      <c r="C285" s="3"/>
+      <c r="D285" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E285" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F285" s="3" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="286" spans="2:6">
-      <c r="B286" s="2" t="s">
+      <c r="B286" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C286" s="3"/>
+      <c r="D286" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E286" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F286" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="C286" s="2"/>
-      <c r="D286" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F286" s="2" t="s">
-        <v>378</v>
-      </c>
     </row>
     <row r="287" spans="2:6">
-      <c r="B287" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="C287" s="2"/>
-      <c r="D287" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E287" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F287" s="2" t="s">
-        <v>378</v>
+      <c r="B287" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C287" s="3"/>
+      <c r="D287" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E287" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F287" s="3" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="288" spans="2:6">
-      <c r="B288" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="C288" s="2"/>
-      <c r="D288" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F288" s="2" t="s">
+      <c r="B288" s="3" t="s">
         <v>383</v>
       </c>
+      <c r="C288" s="3"/>
+      <c r="D288" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E288" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="289" spans="2:6">
-      <c r="B289" s="2" t="s">
+      <c r="B289" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="C289" s="2"/>
-      <c r="D289" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>383</v>
+      <c r="C289" s="3"/>
+      <c r="D289" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E289" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F289" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="290" spans="2:6">
-      <c r="B290" s="2" t="s">
+      <c r="B290" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C290" s="3"/>
+      <c r="D290" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E290" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F290" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C290" s="2"/>
-      <c r="D290" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>383</v>
-      </c>
     </row>
     <row r="291" spans="2:6">
-      <c r="B291" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="C291" s="2"/>
-      <c r="D291" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E291" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F291" s="2" t="s">
-        <v>383</v>
+      <c r="B291" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C291" s="3"/>
+      <c r="D291" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E291" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F291" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="292" spans="2:6">
-      <c r="B292" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C292" s="2"/>
-      <c r="D292" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>182</v>
+      <c r="B292" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C292" s="3"/>
+      <c r="D292" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E292" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="293" spans="2:6">
-      <c r="B293" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C293" s="2"/>
-      <c r="D293" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E293" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>182</v>
+      <c r="B293" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C293" s="3"/>
+      <c r="D293" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="294" spans="2:6">
-      <c r="B294" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C294" s="2"/>
-      <c r="D294" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E294" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>182</v>
+      <c r="B294" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C294" s="3"/>
+      <c r="D294" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E294" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="295" spans="2:6">
-      <c r="B295" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C295" s="2"/>
-      <c r="D295" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E295" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F295" s="2" t="s">
-        <v>182</v>
+      <c r="B295" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C295" s="3"/>
+      <c r="D295" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E295" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F295" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="296" spans="2:6">
-      <c r="B296" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C296" s="2"/>
-      <c r="D296" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E296" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F296" s="2" t="s">
+      <c r="B296" s="3" t="s">
         <v>392</v>
       </c>
+      <c r="C296" s="3"/>
+      <c r="D296" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E296" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F296" s="3" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="297" spans="2:6">
-      <c r="B297" s="2" t="s">
+      <c r="B297" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C297" s="2"/>
-      <c r="D297" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E297" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F297" s="2" t="s">
-        <v>392</v>
+      <c r="C297" s="3"/>
+      <c r="D297" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F297" s="3" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="298" spans="2:6">
-      <c r="B298" s="2" t="s">
+      <c r="B298" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C298" s="3"/>
+      <c r="D298" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F298" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C298" s="2"/>
-      <c r="D298" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>392</v>
-      </c>
     </row>
     <row r="299" spans="2:6">
-      <c r="B299" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C299" s="2"/>
-      <c r="D299" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E299" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F299" s="2" t="s">
-        <v>392</v>
+      <c r="B299" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C299" s="3"/>
+      <c r="D299" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E299" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="300" spans="2:6">
-      <c r="B300" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C300" s="2"/>
-      <c r="D300" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E300" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F300" s="2" t="s">
+      <c r="B300" s="3" t="s">
         <v>397</v>
       </c>
+      <c r="C300" s="3"/>
+      <c r="D300" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E300" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="301" spans="2:6">
-      <c r="B301" s="2" t="s">
+      <c r="B301" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C301" s="2"/>
-      <c r="D301" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E301" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F301" s="2" t="s">
-        <v>397</v>
+      <c r="C301" s="3"/>
+      <c r="D301" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E301" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="302" spans="2:6">
-      <c r="B302" s="2" t="s">
+      <c r="B302" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C302" s="3"/>
+      <c r="D302" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E302" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F302" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="C302" s="2"/>
-      <c r="D302" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E302" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F302" s="2" t="s">
-        <v>397</v>
-      </c>
     </row>
     <row r="303" spans="2:6">
-      <c r="B303" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="C303" s="2"/>
-      <c r="D303" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E303" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>397</v>
+      <c r="B303" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C303" s="3"/>
+      <c r="D303" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E303" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="304" spans="2:6">
-      <c r="B304" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C304" s="2"/>
-      <c r="D304" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E304" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F304" s="2" t="s">
+      <c r="B304" s="3" t="s">
         <v>402</v>
       </c>
+      <c r="C304" s="3"/>
+      <c r="D304" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E304" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>399</v>
+      </c>
     </row>
     <row r="305" spans="2:6">
-      <c r="B305" s="2" t="s">
+      <c r="B305" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C305" s="2"/>
-      <c r="D305" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E305" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F305" s="2" t="s">
-        <v>402</v>
+      <c r="C305" s="3"/>
+      <c r="D305" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E305" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="306" spans="2:6">
-      <c r="B306" s="2" t="s">
+      <c r="B306" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C306" s="3"/>
+      <c r="D306" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E306" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F306" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C306" s="2"/>
-      <c r="D306" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E306" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>402</v>
-      </c>
     </row>
     <row r="307" spans="2:6">
-      <c r="B307" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C307" s="2"/>
-      <c r="D307" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E307" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F307" s="2" t="s">
-        <v>402</v>
+      <c r="B307" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C307" s="3"/>
+      <c r="D307" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E307" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="308" spans="2:6">
-      <c r="B308" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C308" s="2"/>
-      <c r="D308" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E308" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F308" s="2" t="s">
+      <c r="B308" s="3" t="s">
         <v>407</v>
       </c>
+      <c r="C308" s="3"/>
+      <c r="D308" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E308" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F308" s="3" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="309" spans="2:6">
-      <c r="B309" s="2" t="s">
+      <c r="B309" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C309" s="2"/>
-      <c r="D309" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E309" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F309" s="2" t="s">
-        <v>407</v>
+      <c r="C309" s="3"/>
+      <c r="D309" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E309" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F309" s="3" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="310" spans="2:6">
-      <c r="B310" s="2" t="s">
+      <c r="B310" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C310" s="3"/>
+      <c r="D310" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E310" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F310" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="C310" s="2"/>
-      <c r="D310" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E310" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F310" s="2" t="s">
-        <v>407</v>
-      </c>
     </row>
     <row r="311" spans="2:6">
-      <c r="B311" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C311" s="2"/>
-      <c r="D311" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E311" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F311" s="2" t="s">
-        <v>407</v>
+      <c r="B311" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C311" s="3"/>
+      <c r="D311" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E311" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F311" s="3" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="312" spans="2:6">
-      <c r="B312" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C312" s="2"/>
-      <c r="D312" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E312" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F312" s="2" t="s">
+      <c r="B312" s="3" t="s">
         <v>412</v>
       </c>
+      <c r="C312" s="3"/>
+      <c r="D312" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E312" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F312" s="3" t="s">
+        <v>409</v>
+      </c>
     </row>
     <row r="313" spans="2:6">
-      <c r="B313" s="2" t="s">
+      <c r="B313" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C313" s="2"/>
-      <c r="D313" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E313" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F313" s="2" t="s">
-        <v>412</v>
+      <c r="C313" s="3"/>
+      <c r="D313" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F313" s="3" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="314" spans="2:6">
-      <c r="B314" s="2" t="s">
+      <c r="B314" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C314" s="3"/>
+      <c r="D314" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E314" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F314" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C314" s="2"/>
-      <c r="D314" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E314" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>412</v>
-      </c>
     </row>
     <row r="315" spans="2:6">
-      <c r="B315" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C315" s="2"/>
-      <c r="D315" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E315" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F315" s="2" t="s">
-        <v>412</v>
+      <c r="B315" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C315" s="3"/>
+      <c r="D315" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E315" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F315" s="3" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="316" spans="2:6">
-      <c r="B316" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C316" s="2"/>
-      <c r="D316" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F316" s="2" t="s">
+      <c r="B316" s="3" t="s">
         <v>417</v>
       </c>
+      <c r="C316" s="3"/>
+      <c r="D316" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E316" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F316" s="3" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="317" spans="2:6">
-      <c r="B317" s="2" t="s">
+      <c r="B317" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C317" s="2"/>
-      <c r="D317" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E317" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F317" s="2" t="s">
-        <v>417</v>
+      <c r="C317" s="3"/>
+      <c r="D317" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E317" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F317" s="3" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="318" spans="2:6">
-      <c r="B318" s="2" t="s">
+      <c r="B318" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C318" s="3"/>
+      <c r="D318" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E318" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F318" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="C318" s="2"/>
-      <c r="D318" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F318" s="2" t="s">
-        <v>417</v>
-      </c>
     </row>
     <row r="319" spans="2:6">
-      <c r="B319" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C319" s="2"/>
-      <c r="D319" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E319" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F319" s="2" t="s">
-        <v>417</v>
+      <c r="B319" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C319" s="3"/>
+      <c r="D319" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E319" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F319" s="3" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="320" spans="2:6">
-      <c r="B320" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="C320" s="2"/>
-      <c r="D320" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E320" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F320" s="2" t="s">
-        <v>417</v>
+      <c r="B320" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C320" s="3"/>
+      <c r="D320" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E320" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F320" s="3" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="321" spans="2:6">
-      <c r="B321" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="C321" s="2"/>
-      <c r="D321" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E321" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F321" s="2" t="s">
-        <v>417</v>
+      <c r="B321" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C321" s="3"/>
+      <c r="D321" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E321" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F321" s="3" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="322" spans="2:6">
-      <c r="B322" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C322" s="2"/>
-      <c r="D322" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E322" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F322" s="2" t="s">
-        <v>417</v>
+      <c r="B322" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C322" s="3"/>
+      <c r="D322" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E322" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F322" s="3" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="323" spans="2:6">
-      <c r="B323" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="C323" s="2"/>
-      <c r="D323" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E323" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F323" s="2" t="s">
-        <v>417</v>
+      <c r="B323" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C323" s="3"/>
+      <c r="D323" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E323" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F323" s="3" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="324" spans="2:6">
-      <c r="B324" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="C324" s="2"/>
-      <c r="D324" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E324" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F324" s="2" t="s">
+      <c r="B324" s="3" t="s">
         <v>426</v>
       </c>
+      <c r="C324" s="3"/>
+      <c r="D324" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E324" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F324" s="3" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="325" spans="2:6">
-      <c r="B325" s="2" t="s">
+      <c r="B325" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="C325" s="2"/>
-      <c r="D325" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E325" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F325" s="2" t="s">
-        <v>426</v>
+      <c r="C325" s="3"/>
+      <c r="D325" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E325" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F325" s="3" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="326" spans="2:6">
-      <c r="B326" s="2" t="s">
+      <c r="B326" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C326" s="3"/>
+      <c r="D326" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E326" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F326" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="C326" s="2"/>
-      <c r="D326" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E326" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F326" s="2" t="s">
-        <v>426</v>
-      </c>
     </row>
     <row r="327" spans="2:6">
-      <c r="B327" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C327" s="2"/>
-      <c r="D327" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E327" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F327" s="2" t="s">
-        <v>426</v>
+      <c r="B327" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C327" s="3"/>
+      <c r="D327" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E327" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F327" s="3" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="328" spans="2:6">
-      <c r="B328" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="C328" s="2"/>
-      <c r="D328" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E328" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F328" s="2" t="s">
+      <c r="B328" s="3" t="s">
         <v>431</v>
       </c>
+      <c r="C328" s="3"/>
+      <c r="D328" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E328" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F328" s="3" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="329" spans="2:6">
-      <c r="B329" s="2" t="s">
+      <c r="B329" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="C329" s="2"/>
-      <c r="D329" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E329" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F329" s="2" t="s">
-        <v>431</v>
+      <c r="C329" s="3"/>
+      <c r="D329" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E329" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F329" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="330" spans="2:6">
-      <c r="B330" s="2" t="s">
+      <c r="B330" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C330" s="3"/>
+      <c r="D330" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E330" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F330" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="C330" s="2"/>
-      <c r="D330" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E330" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F330" s="2" t="s">
-        <v>431</v>
-      </c>
     </row>
     <row r="331" spans="2:6">
-      <c r="B331" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="C331" s="2"/>
-      <c r="D331" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E331" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F331" s="2" t="s">
-        <v>431</v>
+      <c r="B331" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C331" s="3"/>
+      <c r="D331" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E331" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F331" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="332" spans="2:6">
-      <c r="B332" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="C332" s="2"/>
-      <c r="D332" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E332" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F332" s="2" t="s">
-        <v>431</v>
+      <c r="B332" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C332" s="3"/>
+      <c r="D332" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E332" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F332" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="333" spans="2:6">
-      <c r="B333" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C333" s="2"/>
-      <c r="D333" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E333" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F333" s="2" t="s">
-        <v>431</v>
+      <c r="B333" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C333" s="3"/>
+      <c r="D333" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E333" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F333" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="334" spans="2:6">
-      <c r="B334" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C334" s="2"/>
-      <c r="D334" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E334" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F334" s="2" t="s">
-        <v>431</v>
+      <c r="B334" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C334" s="3"/>
+      <c r="D334" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E334" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F334" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="335" spans="2:6">
-      <c r="B335" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C335" s="2"/>
-      <c r="D335" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E335" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F335" s="2" t="s">
-        <v>431</v>
+      <c r="B335" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C335" s="3"/>
+      <c r="D335" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E335" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F335" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="336" spans="2:6">
-      <c r="B336" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C336" s="2"/>
-      <c r="D336" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E336" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F336" s="2" t="s">
-        <v>431</v>
+      <c r="B336" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C336" s="3"/>
+      <c r="D336" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E336" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F336" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="337" spans="2:6">
-      <c r="B337" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="C337" s="2"/>
-      <c r="D337" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E337" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F337" s="2" t="s">
-        <v>431</v>
+      <c r="B337" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C337" s="3"/>
+      <c r="D337" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E337" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F337" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="338" spans="2:6">
-      <c r="B338" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C338" s="2"/>
-      <c r="D338" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E338" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F338" s="2" t="s">
-        <v>431</v>
+      <c r="B338" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C338" s="3"/>
+      <c r="D338" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E338" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F338" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="339" spans="2:6">
-      <c r="B339" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="C339" s="2"/>
-      <c r="D339" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E339" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F339" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="355" spans="2:6">
-      <c r="B355" s="2" t="s">
+      <c r="B339" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="C355" s="2"/>
-      <c r="D355" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E355" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F355" s="2" t="s">
+      <c r="C339" s="3"/>
+      <c r="D339" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E339" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F339" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="340" spans="2:6">
+      <c r="B340" s="3" t="s">
         <v>444</v>
       </c>
+      <c r="C340" s="3"/>
+      <c r="D340" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E340" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F340" s="3" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="356" spans="2:6">
-      <c r="B356" s="2" t="s">
+      <c r="B356" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="C356" s="2"/>
-      <c r="D356" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E356" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F356" s="2" t="s">
-        <v>444</v>
+      <c r="C356" s="3"/>
+      <c r="D356" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E356" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F356" s="3" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="357" spans="2:6">
-      <c r="B357" s="2" t="s">
+      <c r="B357" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="C357" s="3"/>
+      <c r="D357" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E357" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F357" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="C357" s="2"/>
-      <c r="D357" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E357" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F357" s="2" t="s">
-        <v>444</v>
-      </c>
     </row>
     <row r="358" spans="2:6">
-      <c r="B358" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C358" s="2"/>
-      <c r="D358" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E358" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F358" s="2" t="s">
-        <v>444</v>
+      <c r="B358" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C358" s="3"/>
+      <c r="D358" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E358" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F358" s="3" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="359" spans="2:6">
-      <c r="B359" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C359" s="2"/>
-      <c r="D359" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E359" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F359" s="2" t="s">
+      <c r="B359" s="3" t="s">
         <v>449</v>
       </c>
+      <c r="C359" s="3"/>
+      <c r="D359" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E359" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F359" s="3" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="360" spans="2:6">
-      <c r="B360" s="2" t="s">
+      <c r="B360" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C360" s="2"/>
-      <c r="D360" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E360" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F360" s="2" t="s">
-        <v>449</v>
+      <c r="C360" s="3"/>
+      <c r="D360" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E360" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F360" s="3" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="361" spans="2:6">
-      <c r="B361" s="2" t="s">
+      <c r="B361" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C361" s="3"/>
+      <c r="D361" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E361" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F361" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="C361" s="2"/>
-      <c r="D361" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E361" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F361" s="2" t="s">
-        <v>449</v>
-      </c>
     </row>
     <row r="362" spans="2:6">
-      <c r="B362" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C362" s="2"/>
-      <c r="D362" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E362" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F362" s="2" t="s">
-        <v>449</v>
+      <c r="B362" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C362" s="3"/>
+      <c r="D362" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E362" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F362" s="3" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="363" spans="2:6">
-      <c r="B363" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C363" s="2"/>
-      <c r="D363" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E363" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F363" s="2" t="s">
-        <v>449</v>
+      <c r="B363" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C363" s="3"/>
+      <c r="D363" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E363" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F363" s="3" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="364" spans="2:6">
-      <c r="B364" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="C364" s="2"/>
-      <c r="D364" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E364" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F364" s="2" t="s">
-        <v>449</v>
+      <c r="B364" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C364" s="3"/>
+      <c r="D364" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E364" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F364" s="3" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="365" spans="2:6">
-      <c r="B365" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C365" s="2"/>
-      <c r="D365" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E365" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F365" s="2" t="s">
-        <v>449</v>
+      <c r="B365" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C365" s="3"/>
+      <c r="D365" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E365" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F365" s="3" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="366" spans="2:6">
-      <c r="B366" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="C366" s="2"/>
-      <c r="D366" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E366" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F366" s="2" t="s">
-        <v>449</v>
+      <c r="B366" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C366" s="3"/>
+      <c r="D366" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E366" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F366" s="3" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="367" spans="2:6">
-      <c r="B367" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C367" s="2"/>
-      <c r="D367" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E367" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F367" s="2" t="s">
-        <v>449</v>
+      <c r="B367" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C367" s="3"/>
+      <c r="D367" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E367" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F367" s="3" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="368" spans="2:6">
-      <c r="B368" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C368" s="2"/>
-      <c r="D368" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E368" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F368" s="2" t="s">
-        <v>449</v>
+      <c r="B368" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C368" s="3"/>
+      <c r="D368" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E368" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F368" s="3" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="369" spans="2:6">
-      <c r="B369" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C369" s="2"/>
-      <c r="D369" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E369" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F369" s="2" t="s">
-        <v>449</v>
+      <c r="B369" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C369" s="3"/>
+      <c r="D369" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E369" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F369" s="3" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="370" spans="2:6">
-      <c r="B370" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="C370" s="2"/>
-      <c r="D370" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E370" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F370" s="2" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="387" spans="2:6">
-      <c r="B387" s="2" t="s">
+      <c r="B370" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="C387" s="2"/>
-      <c r="D387" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E387" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F387" s="2" t="s">
+      <c r="C370" s="3"/>
+      <c r="D370" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E370" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F370" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="371" spans="2:6">
+      <c r="B371" s="3" t="s">
         <v>462</v>
       </c>
+      <c r="C371" s="3"/>
+      <c r="D371" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E371" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F371" s="3" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="388" spans="2:6">
-      <c r="B388" s="2" t="s">
+      <c r="B388" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="C388" s="2"/>
-      <c r="D388" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E388" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F388" s="2" t="s">
+      <c r="C388" s="3"/>
+      <c r="D388" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E388" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F388" s="3" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="389" spans="2:6">
-      <c r="B389" s="2" t="s">
+      <c r="B389" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="C389" s="2"/>
-      <c r="D389" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E389" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F389" s="2" t="s">
-        <v>464</v>
+      <c r="C389" s="3"/>
+      <c r="D389" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E389" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F389" s="3" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="390" spans="2:6">
-      <c r="B390" s="2" t="s">
+      <c r="B390" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C390" s="3"/>
+      <c r="D390" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E390" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F390" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="C390" s="2"/>
-      <c r="D390" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E390" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F390" s="2" t="s">
-        <v>464</v>
-      </c>
     </row>
     <row r="391" spans="2:6">
-      <c r="B391" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="C391" s="2"/>
-      <c r="D391" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E391" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F391" s="2" t="s">
+      <c r="B391" s="3" t="s">
         <v>468</v>
       </c>
+      <c r="C391" s="3"/>
+      <c r="D391" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E391" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F391" s="3" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="392" spans="2:6">
-      <c r="B392" s="2" t="s">
+      <c r="B392" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="C392" s="2"/>
-      <c r="D392" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E392" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F392" s="2" t="s">
-        <v>468</v>
+      <c r="C392" s="3"/>
+      <c r="D392" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E392" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F392" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="393" spans="2:6">
-      <c r="B393" s="2" t="s">
+      <c r="B393" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C393" s="3"/>
+      <c r="D393" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E393" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F393" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="C393" s="2"/>
-      <c r="D393" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E393" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F393" s="2" t="s">
-        <v>468</v>
-      </c>
     </row>
     <row r="394" spans="2:6">
-      <c r="B394" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="C394" s="2"/>
-      <c r="D394" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E394" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F394" s="2" t="s">
-        <v>468</v>
+      <c r="B394" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C394" s="3"/>
+      <c r="D394" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E394" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F394" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="395" spans="2:6">
-      <c r="B395" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C395" s="2"/>
-      <c r="D395" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E395" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F395" s="2" t="s">
-        <v>468</v>
+      <c r="B395" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C395" s="3"/>
+      <c r="D395" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E395" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F395" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="396" spans="2:6">
-      <c r="B396" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="C396" s="2"/>
-      <c r="D396" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E396" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F396" s="2" t="s">
-        <v>468</v>
+      <c r="B396" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C396" s="3"/>
+      <c r="D396" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E396" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F396" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="397" spans="2:6">
-      <c r="B397" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="C397" s="2"/>
-      <c r="D397" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E397" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F397" s="2" t="s">
-        <v>468</v>
+      <c r="B397" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C397" s="3"/>
+      <c r="D397" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E397" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F397" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="398" spans="2:6">
-      <c r="B398" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="C398" s="2"/>
-      <c r="D398" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E398" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F398" s="2" t="s">
-        <v>468</v>
+      <c r="B398" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C398" s="3"/>
+      <c r="D398" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E398" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F398" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="399" spans="2:6">
-      <c r="B399" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="C399" s="2"/>
-      <c r="D399" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E399" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F399" s="2" t="s">
-        <v>468</v>
+      <c r="B399" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C399" s="3"/>
+      <c r="D399" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E399" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F399" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="400" spans="2:6">
-      <c r="B400" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="C400" s="2"/>
-      <c r="D400" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E400" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F400" s="2" t="s">
-        <v>468</v>
+      <c r="B400" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C400" s="3"/>
+      <c r="D400" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E400" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F400" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="401" spans="2:6">
-      <c r="B401" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="C401" s="2"/>
-      <c r="D401" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E401" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F401" s="2" t="s">
-        <v>468</v>
+      <c r="B401" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C401" s="3"/>
+      <c r="D401" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E401" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F401" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="402" spans="2:6">
-      <c r="B402" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="C402" s="2"/>
-      <c r="D402" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E402" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F402" s="2" t="s">
-        <v>468</v>
+      <c r="B402" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C402" s="3"/>
+      <c r="D402" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E402" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F402" s="3" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="403" spans="2:6">
-      <c r="B403" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="C403" s="2"/>
-      <c r="D403" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E403" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F403" s="2" t="s">
+      <c r="B403" s="3" t="s">
         <v>481</v>
       </c>
+      <c r="C403" s="3"/>
+      <c r="D403" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E403" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F403" s="3" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="404" spans="2:6">
-      <c r="B404" s="2" t="s">
+      <c r="B404" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="C404" s="2"/>
-      <c r="D404" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E404" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F404" s="2" t="s">
-        <v>481</v>
+      <c r="C404" s="3"/>
+      <c r="D404" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E404" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F404" s="3" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="405" spans="2:6">
-      <c r="B405" s="2" t="s">
+      <c r="B405" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C405" s="3"/>
+      <c r="D405" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E405" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F405" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C405" s="2"/>
-      <c r="D405" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E405" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F405" s="2" t="s">
-        <v>481</v>
-      </c>
     </row>
     <row r="406" spans="2:6">
-      <c r="B406" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="C406" s="2"/>
-      <c r="D406" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E406" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F406" s="2" t="s">
-        <v>481</v>
+      <c r="B406" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C406" s="3"/>
+      <c r="D406" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E406" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F406" s="3" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="407" spans="2:6">
-      <c r="B407" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C407" s="2"/>
-      <c r="D407" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E407" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F407" s="2" t="s">
-        <v>481</v>
+      <c r="B407" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C407" s="3"/>
+      <c r="D407" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E407" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F407" s="3" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="408" spans="2:6">
-      <c r="B408" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="C408" s="2"/>
-      <c r="D408" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E408" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F408" s="2" t="s">
-        <v>481</v>
+      <c r="B408" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C408" s="3"/>
+      <c r="D408" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E408" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F408" s="3" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="409" spans="2:6">
-      <c r="B409" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="C409" s="2"/>
-      <c r="D409" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E409" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F409" s="2" t="s">
-        <v>481</v>
+      <c r="B409" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C409" s="3"/>
+      <c r="D409" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E409" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F409" s="3" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="410" spans="2:6">
-      <c r="B410" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="C410" s="2"/>
-      <c r="D410" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E410" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F410" s="2" t="s">
-        <v>481</v>
+      <c r="B410" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C410" s="3"/>
+      <c r="D410" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E410" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F410" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="411" spans="2:6">
+      <c r="B411" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C411" s="3"/>
+      <c r="D411" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E411" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F411" s="3" t="s">
+        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/rag/意图泛化语料.xlsx
+++ b/src/main/resources/rag/意图泛化语料.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="520"/>
+    <workbookView windowWidth="22188" windowHeight="9060" tabRatio="520" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet name="通用" sheetId="1" r:id="rId1"/>
+    <sheet name="未授信" sheetId="2" r:id="rId2"/>
+    <sheet name="已授信" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="497">
   <si>
     <t>历史提问</t>
   </si>
@@ -1410,10 +1412,94 @@
     <t>借不到那么多金额怎么处理？</t>
   </si>
   <si>
+    <t>我怎么能借的钱那么少；</t>
+  </si>
+  <si>
+    <t>您好，根据系统查询，您目前的最大可借额度为${maxPrice}，实际借款金额以审批为准，您本次需要借多少呢？</t>
+  </si>
+  <si>
+    <t>为什么我的借款额度这么低？</t>
+  </si>
+  <si>
+    <t>您好，根据系统查询，您目前的最大可借额度为${maxPrice}，您本次需要借多少呢？</t>
+  </si>
+  <si>
+    <t>怎么我只能借这么少的钱？</t>
+  </si>
+  <si>
+    <t>我的贷款金额为什么那么少？</t>
+  </si>
+  <si>
+    <t>换我另一张卡</t>
+  </si>
+  <si>
+    <t>尊敬的客户，此次借款业务中，为了保障您的交易安全性，【马小i】建议您直接在借款卡片中更换或调整您的银行卡</t>
+  </si>
+  <si>
+    <t>可以换成我的另一张银行卡吗？</t>
+  </si>
+  <si>
+    <t>我想用别的银行卡可以吗？</t>
+  </si>
+  <si>
+    <t>能更换另一张卡吗？</t>
+  </si>
+  <si>
+    <t>换工商那张卡</t>
+  </si>
+  <si>
+    <t>可以用我的工商银行卡吗？</t>
+  </si>
+  <si>
+    <t>我想换成工商银行的卡可以吗？</t>
+  </si>
+  <si>
+    <t>能换成我的工商卡吗？</t>
+  </si>
+  <si>
+    <t>换我8805那张卡</t>
+  </si>
+  <si>
+    <t>可以用我尾号8805的卡吗？</t>
+  </si>
+  <si>
+    <t>我想换成尾号8805的银行卡可以吗？</t>
+  </si>
+  <si>
+    <t>能更换成尾号8805的卡吗？</t>
+  </si>
+  <si>
+    <t>可以用优惠券么</t>
+  </si>
+  <si>
+    <t>【马小i】提示：若您有可用的优惠券，您可以直接在借款卡片中选择您要使用的优惠券</t>
+  </si>
+  <si>
+    <t>借款可以用优惠券吗？</t>
+  </si>
+  <si>
+    <t>贷款支持使用优惠券吗？</t>
+  </si>
+  <si>
+    <t>能用优惠券抵扣吗？</t>
+  </si>
+  <si>
+    <t>可以减免么</t>
+  </si>
+  <si>
+    <t>贷款可以减免费用吗？</t>
+  </si>
+  <si>
+    <t>有没有减免的政策？</t>
+  </si>
+  <si>
+    <t>借款能减免部分费用吗？</t>
+  </si>
+  <si>
     <t>贷款可以分成多少期</t>
   </si>
   <si>
-    <t>目前您可以选择的分期期数为${terms} ，您可以告诉【马小i】您想选择多少期呢？</t>
+    <t>我们提供的分期选项通常有3/6/9/12等多种选择，具体可能会根据品、借款渠道、终端（如小程序、APP）不同会有所差异。若您需要申请借款，在授信通过后您可以咨询小优您具体的可选期数。</t>
   </si>
   <si>
     <t>借款可以分几期还？</t>
@@ -1437,100 +1523,34 @@
     <t>你们的贷款还款期限是多久？</t>
   </si>
   <si>
+    <t>我们提供的分期选项通常有3/6/9/13等多种选择，具体可能会根据品、借款渠道、终端（如小程序、APP）不同会有所差异。若您需要申请借款，在授信通过后您可以咨询小优您具体的可选期数。</t>
+  </si>
+  <si>
     <t>给我调整下期数，这个每期还的太多了，还不起</t>
   </si>
   <si>
+    <t>我们提供的分期选项通常有3/6/9/14等多种选择，具体可能会根据品、借款渠道、终端（如小程序、APP）不同会有所差异。若您需要申请借款，在授信通过后您可以咨询小优您具体的可选期数。</t>
+  </si>
+  <si>
     <t>能调整一下分期数吗？每期还款太多还不起。</t>
   </si>
   <si>
+    <t>我们提供的分期选项通常有3/6/9/15等多种选择，具体可能会根据品、借款渠道、终端（如小程序、APP）不同会有所差异。若您需要申请借款，在授信通过后您可以咨询小优您具体的可选期数。</t>
+  </si>
+  <si>
     <t>可以改一下期数吗？现在每期还款太高了。</t>
   </si>
   <si>
+    <t>我们提供的分期选项通常有3/6/9/16等多种选择，具体可能会根据品、借款渠道、终端（如小程序、APP）不同会有所差异。若您需要申请借款，在授信通过后您可以咨询小优您具体的可选期数。</t>
+  </si>
+  <si>
     <t>每期还款太多，能不能调整分期数？</t>
   </si>
   <si>
-    <t>我怎么能借的钱那么少；</t>
-  </si>
-  <si>
-    <t>您好，根据系统查询，您目前的最大可借额度为${maxPrice}，实际借款金额以审批为准，您本次需要借多少呢？</t>
-  </si>
-  <si>
-    <t>为什么我的借款额度这么低？</t>
-  </si>
-  <si>
-    <t>您好，根据系统查询，您目前的最大可借额度为${maxPrice}，您本次需要借多少呢？</t>
-  </si>
-  <si>
-    <t>怎么我只能借这么少的钱？</t>
-  </si>
-  <si>
-    <t>我的贷款金额为什么那么少？</t>
-  </si>
-  <si>
-    <t>换我另一张卡</t>
-  </si>
-  <si>
-    <t>尊敬的客户，此次借款业务中，为了保障您的交易安全性，【马小i】建议您直接在借款卡片中更换或调整您的银行卡</t>
-  </si>
-  <si>
-    <t>可以换成我的另一张银行卡吗？</t>
-  </si>
-  <si>
-    <t>我想用别的银行卡可以吗？</t>
-  </si>
-  <si>
-    <t>能更换另一张卡吗？</t>
-  </si>
-  <si>
-    <t>换工商那张卡</t>
-  </si>
-  <si>
-    <t>可以用我的工商银行卡吗？</t>
-  </si>
-  <si>
-    <t>我想换成工商银行的卡可以吗？</t>
-  </si>
-  <si>
-    <t>能换成我的工商卡吗？</t>
-  </si>
-  <si>
-    <t>换我8805那张卡</t>
-  </si>
-  <si>
-    <t>可以用我尾号8805的卡吗？</t>
-  </si>
-  <si>
-    <t>我想换成尾号8805的银行卡可以吗？</t>
-  </si>
-  <si>
-    <t>能更换成尾号8805的卡吗？</t>
-  </si>
-  <si>
-    <t>可以用优惠券么</t>
-  </si>
-  <si>
-    <t>【马小i】提示：若您有可用的优惠券，您可以直接在借款卡片中选择您要使用的优惠券</t>
-  </si>
-  <si>
-    <t>借款可以用优惠券吗？</t>
-  </si>
-  <si>
-    <t>贷款支持使用优惠券吗？</t>
-  </si>
-  <si>
-    <t>能用优惠券抵扣吗？</t>
-  </si>
-  <si>
-    <t>可以减免么</t>
-  </si>
-  <si>
-    <t>贷款可以减免费用吗？</t>
-  </si>
-  <si>
-    <t>有没有减免的政策？</t>
-  </si>
-  <si>
-    <t>借款能减免部分费用吗？</t>
+    <t>我们提供的分期选项通常有3/6/9/17等多种选择，具体可能会根据品、借款渠道、终端（如小程序、APP）不同会有所差异。若您需要申请借款，在授信通过后您可以咨询小优您具体的可选期数。</t>
+  </si>
+  <si>
+    <t>客户您好，根据系统查询，若您想要申请借款，您目前可申请的分期数为${terms}</t>
   </si>
 </sst>
 </file>
@@ -2171,10 +2191,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2521,7 +2541,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F411"/>
+  <dimension ref="A1:F368"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="47.2222222222222" customWidth="1"/>
@@ -2613,7 +2633,7 @@
       </c>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>3500</v>
       </c>
       <c r="C5" t="s">
@@ -3350,10 +3370,10 @@
       </c>
     </row>
     <row r="42" spans="2:6">
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D42" t="s">
@@ -3367,10 +3387,10 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D43" t="s">
@@ -3384,10 +3404,10 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D44" t="s">
@@ -3401,10 +3421,10 @@
       </c>
     </row>
     <row r="45" spans="2:6">
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D45" t="s">
@@ -3418,10 +3438,10 @@
       </c>
     </row>
     <row r="46" spans="2:6">
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D46" t="s">
@@ -3435,10 +3455,10 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D47" t="s">
@@ -3452,10 +3472,10 @@
       </c>
     </row>
     <row r="48" spans="2:6">
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D48" t="s">
@@ -3469,10 +3489,10 @@
       </c>
     </row>
     <row r="49" spans="2:6">
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D49" t="s">
@@ -3486,10 +3506,10 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D50" t="s">
@@ -3503,10 +3523,10 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D51" t="s">
@@ -3520,10 +3540,10 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D52" t="s">
@@ -3537,10 +3557,10 @@
       </c>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>92</v>
       </c>
       <c r="D53" t="s">
@@ -3554,10 +3574,10 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D54" t="s">
@@ -3571,10 +3591,10 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D55" t="s">
@@ -3588,10 +3608,10 @@
       </c>
     </row>
     <row r="56" spans="2:6">
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>105</v>
       </c>
       <c r="D56" t="s">
@@ -3605,16 +3625,16 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D57" t="s">
         <v>9</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F57" t="s">
@@ -3622,16 +3642,16 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D58" t="s">
         <v>9</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F58" t="s">
@@ -3639,16 +3659,16 @@
       </c>
     </row>
     <row r="59" spans="2:6">
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D59" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F59" t="s">
@@ -3656,16 +3676,16 @@
       </c>
     </row>
     <row r="60" spans="2:6">
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D60" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F60" t="s">
@@ -3673,16 +3693,16 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D61" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E61" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F61" t="s">
@@ -3690,16 +3710,16 @@
       </c>
     </row>
     <row r="62" spans="2:6">
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D62" t="s">
         <v>9</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F62" t="s">
@@ -3707,16 +3727,16 @@
       </c>
     </row>
     <row r="63" spans="2:6">
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D63" t="s">
         <v>9</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F63" t="s">
@@ -3724,16 +3744,16 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D64" t="s">
         <v>9</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F64" t="s">
@@ -3741,16 +3761,16 @@
       </c>
     </row>
     <row r="65" spans="2:6">
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D65" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F65" t="s">
@@ -3758,16 +3778,16 @@
       </c>
     </row>
     <row r="66" spans="2:6">
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D66" t="s">
         <v>9</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F66" t="s">
@@ -3775,16 +3795,16 @@
       </c>
     </row>
     <row r="67" spans="2:6">
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D67" t="s">
         <v>9</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F67" t="s">
@@ -3792,16 +3812,16 @@
       </c>
     </row>
     <row r="68" spans="2:6">
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D68" t="s">
         <v>9</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F68" t="s">
@@ -3809,16 +3829,16 @@
       </c>
     </row>
     <row r="69" spans="2:6">
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D69" t="s">
         <v>9</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F69" t="s">
@@ -3826,16 +3846,16 @@
       </c>
     </row>
     <row r="70" spans="2:6">
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F70" t="s">
@@ -3843,16 +3863,16 @@
       </c>
     </row>
     <row r="71" spans="2:6">
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D71" t="s">
         <v>9</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F71" t="s">
@@ -3860,16 +3880,16 @@
       </c>
     </row>
     <row r="72" spans="2:6">
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D72" t="s">
         <v>9</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F72" t="s">
@@ -3877,4623 +3897,4916 @@
       </c>
     </row>
     <row r="73" spans="2:6">
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F73" s="3" t="s">
+      <c r="C73" s="2"/>
+      <c r="D73" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="74" spans="2:6">
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F74" s="3" t="s">
+      <c r="C74" s="2"/>
+      <c r="D74" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="75" spans="2:6">
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F75" s="3" t="s">
+      <c r="C75" s="2"/>
+      <c r="D75" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F76" s="3" t="s">
+      <c r="C76" s="2"/>
+      <c r="D76" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="77" spans="2:6">
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F77" s="3" t="s">
+      <c r="C77" s="2"/>
+      <c r="D77" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="78" spans="2:6">
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F78" s="3" t="s">
+      <c r="C78" s="2"/>
+      <c r="D78" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="79" spans="2:6">
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F79" s="3" t="s">
+      <c r="C79" s="2"/>
+      <c r="D79" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="80" spans="2:6">
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F80" s="3" t="s">
+      <c r="C80" s="2"/>
+      <c r="D80" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F81" s="3" t="s">
+      <c r="C81" s="2"/>
+      <c r="D81" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F81" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="82" spans="2:6">
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F82" s="3" t="s">
+      <c r="C82" s="2"/>
+      <c r="D82" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F82" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="83" spans="2:6">
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F83" s="3" t="s">
+      <c r="C83" s="2"/>
+      <c r="D83" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="84" spans="2:6">
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F84" s="3" t="s">
+      <c r="C84" s="2"/>
+      <c r="D84" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F84" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="85" spans="2:6">
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F85" s="3" t="s">
+      <c r="C85" s="2"/>
+      <c r="D85" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F85" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="86" spans="2:6">
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F86" s="3" t="s">
+      <c r="C86" s="2"/>
+      <c r="D86" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F86" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="87" spans="2:6">
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F87" s="3" t="s">
+      <c r="C87" s="2"/>
+      <c r="D87" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F87" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="88" spans="2:6">
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F88" s="3" t="s">
+      <c r="C88" s="2"/>
+      <c r="D88" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F88" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F89" s="3" t="s">
+      <c r="C89" s="2"/>
+      <c r="D89" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F89" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F90" s="3" t="s">
+      <c r="C90" s="2"/>
+      <c r="D90" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F90" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="91" spans="2:6">
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F91" s="3" t="s">
+      <c r="C91" s="2"/>
+      <c r="D91" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="92" spans="2:6">
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F92" s="3" t="s">
+      <c r="C92" s="2"/>
+      <c r="D92" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F92" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="93" spans="2:6">
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F93" s="3" t="s">
+      <c r="C93" s="2"/>
+      <c r="D93" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F93" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="94" spans="2:6">
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F94" s="3" t="s">
+      <c r="C94" s="2"/>
+      <c r="D94" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="95" spans="2:6">
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F95" s="3" t="s">
+      <c r="C95" s="2"/>
+      <c r="D95" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F95" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="96" spans="2:6">
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F96" s="3" t="s">
+      <c r="C96" s="2"/>
+      <c r="D96" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F97" s="3" t="s">
+      <c r="C97" s="2"/>
+      <c r="D97" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F97" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F98" s="3" t="s">
+      <c r="C98" s="2"/>
+      <c r="D98" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F98" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F99" s="3" t="s">
+      <c r="C99" s="2"/>
+      <c r="D99" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F99" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F100" s="3" t="s">
+      <c r="C100" s="2"/>
+      <c r="D100" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F101" s="3" t="s">
+      <c r="C101" s="2"/>
+      <c r="D101" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="102" spans="2:6">
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F102" s="3" t="s">
+      <c r="C102" s="2"/>
+      <c r="D102" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="103" spans="2:6">
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F103" s="3" t="s">
+      <c r="C103" s="2"/>
+      <c r="D103" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F103" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="104" spans="2:6">
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F104" s="3" t="s">
+      <c r="C104" s="2"/>
+      <c r="D104" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="105" spans="2:6">
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F105" s="3" t="s">
+      <c r="C105" s="2"/>
+      <c r="D105" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F105" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="106" spans="2:6">
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F106" s="3" t="s">
+      <c r="C106" s="2"/>
+      <c r="D106" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F106" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F107" s="3" t="s">
+      <c r="C107" s="2"/>
+      <c r="D107" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F107" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F108" s="3" t="s">
+      <c r="C108" s="2"/>
+      <c r="D108" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F108" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="109" spans="2:6">
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F109" s="3" t="s">
+      <c r="C109" s="2"/>
+      <c r="D109" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F109" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="110" spans="2:6">
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F110" s="3" t="s">
+      <c r="C110" s="2"/>
+      <c r="D110" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F110" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="111" spans="2:6">
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F111" s="3" t="s">
+      <c r="C111" s="2"/>
+      <c r="D111" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F111" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="112" spans="2:6">
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F112" s="3" t="s">
+      <c r="C112" s="2"/>
+      <c r="D112" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F112" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="113" spans="2:6">
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F113" s="3" t="s">
+      <c r="C113" s="2"/>
+      <c r="D113" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F113" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="114" spans="2:6">
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F114" s="3" t="s">
+      <c r="C114" s="2"/>
+      <c r="D114" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F114" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="115" spans="2:6">
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F115" s="3" t="s">
+      <c r="C115" s="2"/>
+      <c r="D115" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F115" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="116" spans="2:6">
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F116" s="3" t="s">
+      <c r="C116" s="2"/>
+      <c r="D116" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F116" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="117" spans="2:6">
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F117" s="3" t="s">
+      <c r="C117" s="2"/>
+      <c r="D117" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F117" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="118" spans="2:6">
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F118" s="3" t="s">
+      <c r="C118" s="2"/>
+      <c r="D118" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F118" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="119" spans="2:6">
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F119" s="3" t="s">
+      <c r="C119" s="2"/>
+      <c r="D119" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F119" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="120" spans="2:6">
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F120" s="3" t="s">
+      <c r="C120" s="2"/>
+      <c r="D120" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F120" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="121" spans="2:6">
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C121" s="3"/>
-      <c r="D121" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F121" s="3" t="s">
+      <c r="C121" s="2"/>
+      <c r="D121" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F121" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="122" spans="2:6">
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C122" s="3"/>
-      <c r="D122" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F122" s="3" t="s">
+      <c r="C122" s="2"/>
+      <c r="D122" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F122" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="123" spans="2:6">
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C123" s="3"/>
-      <c r="D123" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F123" s="3" t="s">
+      <c r="C123" s="2"/>
+      <c r="D123" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F123" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C124" s="3"/>
-      <c r="D124" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F124" s="3" t="s">
+      <c r="C124" s="2"/>
+      <c r="D124" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F124" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="125" spans="2:6">
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C125" s="3"/>
-      <c r="D125" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F125" s="3" t="s">
+      <c r="C125" s="2"/>
+      <c r="D125" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F125" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="126" spans="2:6">
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C126" s="3"/>
-      <c r="D126" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F126" s="3" t="s">
+      <c r="C126" s="2"/>
+      <c r="D126" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F126" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="127" spans="2:6">
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C127" s="3"/>
-      <c r="D127" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E127" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F127" s="3" t="s">
+      <c r="C127" s="2"/>
+      <c r="D127" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F127" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="128" spans="2:6">
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C128" s="3"/>
-      <c r="D128" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E128" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F128" s="3" t="s">
+      <c r="C128" s="2"/>
+      <c r="D128" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F128" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="129" spans="2:6">
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E129" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F129" s="3" t="s">
+      <c r="C129" s="2"/>
+      <c r="D129" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F129" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="130" spans="2:6">
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C130" s="3"/>
-      <c r="D130" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E130" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F130" s="3" t="s">
+      <c r="C130" s="2"/>
+      <c r="D130" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F130" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="131" spans="2:6">
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C131" s="3"/>
-      <c r="D131" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E131" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F131" s="3" t="s">
+      <c r="C131" s="2"/>
+      <c r="D131" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F131" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="132" spans="2:6">
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C132" s="3"/>
-      <c r="D132" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F132" s="3" t="s">
+      <c r="C132" s="2"/>
+      <c r="D132" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F132" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="133" spans="2:6">
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C133" s="3"/>
-      <c r="D133" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F133" s="3" t="s">
+      <c r="C133" s="2"/>
+      <c r="D133" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F133" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="134" spans="2:6">
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C134" s="3"/>
-      <c r="D134" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E134" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F134" s="3" t="s">
+      <c r="C134" s="2"/>
+      <c r="D134" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F134" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="135" spans="2:6">
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C135" s="3"/>
-      <c r="D135" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E135" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F135" s="3" t="s">
+      <c r="C135" s="2"/>
+      <c r="D135" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F135" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="136" spans="2:6">
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C136" s="3"/>
-      <c r="D136" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E136" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F136" s="3" t="s">
+      <c r="C136" s="2"/>
+      <c r="D136" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F136" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="137" spans="2:6">
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C137" s="3"/>
-      <c r="D137" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F137" s="3" t="s">
+      <c r="C137" s="2"/>
+      <c r="D137" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F137" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="138" spans="2:6">
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C138" s="3"/>
-      <c r="D138" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E138" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F138" s="3" t="s">
+      <c r="C138" s="2"/>
+      <c r="D138" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F138" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="139" spans="2:6">
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C139" s="3"/>
-      <c r="D139" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E139" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F139" s="3" t="s">
+      <c r="C139" s="2"/>
+      <c r="D139" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F139" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="140" spans="2:6">
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C140" s="3"/>
-      <c r="D140" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F140" s="3" t="s">
+      <c r="C140" s="2"/>
+      <c r="D140" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F140" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="141" spans="2:6">
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C141" s="3"/>
-      <c r="D141" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F141" s="3" t="s">
+      <c r="C141" s="2"/>
+      <c r="D141" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F141" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="142" spans="2:6">
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C142" s="3"/>
-      <c r="D142" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E142" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F142" s="3" t="s">
+      <c r="C142" s="2"/>
+      <c r="D142" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F142" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="143" spans="2:6">
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C143" s="3"/>
-      <c r="D143" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E143" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F143" s="3" t="s">
+      <c r="C143" s="2"/>
+      <c r="D143" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F143" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="144" spans="2:6">
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C144" s="3"/>
-      <c r="D144" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E144" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F144" s="3" t="s">
+      <c r="C144" s="2"/>
+      <c r="D144" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F144" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="145" spans="2:6">
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C145" s="3"/>
-      <c r="D145" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F145" s="3" t="s">
+      <c r="C145" s="2"/>
+      <c r="D145" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F145" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="146" spans="2:6">
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C146" s="3"/>
-      <c r="D146" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F146" s="3" t="s">
+      <c r="C146" s="2"/>
+      <c r="D146" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F146" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="147" spans="2:6">
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C147" s="3"/>
-      <c r="D147" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F147" s="3" t="s">
+      <c r="C147" s="2"/>
+      <c r="D147" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F147" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="148" spans="2:6">
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C148" s="3"/>
-      <c r="D148" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E148" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F148" s="3" t="s">
+      <c r="C148" s="2"/>
+      <c r="D148" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F148" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="149" spans="2:6">
-      <c r="B149" s="3" t="s">
+      <c r="B149" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C149" s="3"/>
-      <c r="D149" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F149" s="3" t="s">
+      <c r="C149" s="2"/>
+      <c r="D149" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F149" s="2" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="150" spans="2:6">
-      <c r="B150" s="3" t="s">
+      <c r="B150" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C150" s="3"/>
-      <c r="D150" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E150" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F150" s="3" t="s">
+      <c r="C150" s="2"/>
+      <c r="D150" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F150" s="2" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="151" spans="2:6">
-      <c r="B151" s="3" t="s">
+      <c r="B151" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C151" s="3"/>
-      <c r="D151" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E151" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F151" s="3" t="s">
+      <c r="C151" s="2"/>
+      <c r="D151" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F151" s="2" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="152" spans="2:6">
-      <c r="B152" s="3" t="s">
+      <c r="B152" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C152" s="3"/>
-      <c r="D152" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F152" s="3" t="s">
+      <c r="C152" s="2"/>
+      <c r="D152" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F152" s="2" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="153" spans="2:6">
-      <c r="B153" s="3" t="s">
+      <c r="B153" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C153" s="3"/>
-      <c r="D153" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E153" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F153" s="3" t="s">
+      <c r="C153" s="2"/>
+      <c r="D153" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F153" s="2" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="154" spans="2:6">
-      <c r="B154" s="3" t="s">
+      <c r="B154" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C154" s="3"/>
-      <c r="D154" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E154" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F154" s="3" t="s">
+      <c r="C154" s="2"/>
+      <c r="D154" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F154" s="2" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="155" spans="2:6">
-      <c r="B155" s="3" t="s">
+      <c r="B155" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C155" s="3"/>
-      <c r="D155" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F155" s="3" t="s">
+      <c r="C155" s="2"/>
+      <c r="D155" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F155" s="2" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="156" spans="2:6">
-      <c r="B156" s="3" t="s">
+      <c r="B156" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C156" s="3"/>
-      <c r="D156" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F156" s="3" t="s">
+      <c r="C156" s="2"/>
+      <c r="D156" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="157" spans="2:6">
-      <c r="B157" s="3" t="s">
+      <c r="B157" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C157" s="3"/>
-      <c r="D157" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E157" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F157" s="3" t="s">
+      <c r="C157" s="2"/>
+      <c r="D157" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F157" s="2" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="158" spans="2:6">
-      <c r="B158" s="3" t="s">
+      <c r="B158" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C158" s="3"/>
-      <c r="D158" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F158" s="3" t="s">
+      <c r="C158" s="2"/>
+      <c r="D158" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F158" s="2" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="159" spans="2:6">
-      <c r="B159" s="3" t="s">
+      <c r="B159" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C159" s="3"/>
-      <c r="D159" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F159" s="3" t="s">
+      <c r="C159" s="2"/>
+      <c r="D159" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F159" s="2" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="160" spans="2:6">
-      <c r="B160" s="3" t="s">
+      <c r="B160" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C160" s="3"/>
-      <c r="D160" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E160" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F160" s="3" t="s">
+      <c r="C160" s="2"/>
+      <c r="D160" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F160" s="2" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="3" t="s">
+      <c r="B161" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C161" s="3"/>
-      <c r="D161" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E161" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F161" s="3" t="s">
+      <c r="C161" s="2"/>
+      <c r="D161" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F161" s="2" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="3" t="s">
+      <c r="B162" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C162" s="3"/>
-      <c r="D162" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E162" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F162" s="3" t="s">
+      <c r="C162" s="2"/>
+      <c r="D162" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F162" s="2" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="163" spans="2:6">
-      <c r="B163" s="3" t="s">
+      <c r="B163" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C163" s="3"/>
-      <c r="D163" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E163" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F163" s="3" t="s">
+      <c r="C163" s="2"/>
+      <c r="D163" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F163" s="2" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="164" spans="2:6">
-      <c r="B164" s="3" t="s">
+      <c r="B164" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C164" s="3"/>
-      <c r="D164" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E164" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F164" s="3" t="s">
+      <c r="C164" s="2"/>
+      <c r="D164" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F164" s="2" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="165" spans="2:6">
-      <c r="B165" s="3" t="s">
+      <c r="B165" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C165" s="3"/>
-      <c r="D165" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E165" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F165" s="3" t="s">
+      <c r="C165" s="2"/>
+      <c r="D165" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F165" s="2" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="166" spans="2:6">
-      <c r="B166" s="3" t="s">
+      <c r="B166" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C166" s="3"/>
-      <c r="D166" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E166" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F166" s="3" t="s">
+      <c r="C166" s="2"/>
+      <c r="D166" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F166" s="2" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="167" spans="2:6">
-      <c r="B167" s="3" t="s">
+      <c r="B167" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C167" s="3"/>
-      <c r="D167" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E167" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F167" s="3" t="s">
+      <c r="C167" s="2"/>
+      <c r="D167" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F167" s="2" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="168" spans="2:6">
-      <c r="B168" s="3" t="s">
+      <c r="B168" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C168" s="3"/>
-      <c r="D168" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F168" s="3" t="s">
+      <c r="C168" s="2"/>
+      <c r="D168" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="169" spans="2:6">
-      <c r="B169" s="3" t="s">
+      <c r="B169" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C169" s="3"/>
-      <c r="D169" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E169" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F169" s="3" t="s">
+      <c r="C169" s="2"/>
+      <c r="D169" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F169" s="2" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="170" spans="2:6">
-      <c r="B170" s="3" t="s">
+      <c r="B170" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C170" s="3"/>
-      <c r="D170" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E170" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F170" s="3" t="s">
+      <c r="C170" s="2"/>
+      <c r="D170" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F170" s="2" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="171" spans="2:6">
-      <c r="B171" s="3" t="s">
+      <c r="B171" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C171" s="3"/>
-      <c r="D171" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E171" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F171" s="3" t="s">
+      <c r="C171" s="2"/>
+      <c r="D171" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F171" s="2" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="172" spans="2:6">
-      <c r="B172" s="3" t="s">
+      <c r="B172" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C172" s="3"/>
-      <c r="D172" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E172" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F172" s="3" t="s">
+      <c r="C172" s="2"/>
+      <c r="D172" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F172" s="2" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="173" spans="2:6">
-      <c r="B173" s="3" t="s">
+      <c r="B173" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C173" s="3"/>
-      <c r="D173" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E173" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F173" s="3" t="s">
+      <c r="C173" s="2"/>
+      <c r="D173" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F173" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="174" spans="2:6">
-      <c r="B174" s="3" t="s">
+      <c r="B174" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C174" s="3"/>
-      <c r="D174" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E174" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F174" s="3" t="s">
+      <c r="C174" s="2"/>
+      <c r="D174" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F174" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="175" spans="2:6">
-      <c r="B175" s="3" t="s">
+      <c r="B175" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C175" s="3"/>
-      <c r="D175" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E175" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F175" s="3" t="s">
+      <c r="C175" s="2"/>
+      <c r="D175" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F175" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="176" spans="2:6">
-      <c r="B176" s="3" t="s">
+      <c r="B176" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C176" s="3"/>
-      <c r="D176" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E176" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F176" s="3" t="s">
+      <c r="C176" s="2"/>
+      <c r="D176" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F176" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="3" t="s">
+      <c r="B177" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C177" s="3"/>
-      <c r="D177" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E177" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F177" s="3" t="s">
+      <c r="C177" s="2"/>
+      <c r="D177" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F177" s="2" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="178" spans="2:6">
-      <c r="B178" s="3" t="s">
+      <c r="B178" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C178" s="3"/>
-      <c r="D178" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E178" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F178" s="3" t="s">
+      <c r="C178" s="2"/>
+      <c r="D178" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F178" s="2" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="179" spans="2:6">
-      <c r="B179" s="3" t="s">
+      <c r="B179" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C179" s="3"/>
-      <c r="D179" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E179" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F179" s="3" t="s">
+      <c r="C179" s="2"/>
+      <c r="D179" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F179" s="2" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="180" spans="2:6">
-      <c r="B180" s="3" t="s">
+      <c r="B180" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C180" s="3"/>
-      <c r="D180" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E180" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F180" s="3" t="s">
+      <c r="C180" s="2"/>
+      <c r="D180" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F180" s="2" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="181" spans="2:6">
-      <c r="B181" s="3" t="s">
+      <c r="B181" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C181" s="3"/>
-      <c r="D181" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E181" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F181" s="3" t="s">
+      <c r="C181" s="2"/>
+      <c r="D181" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F181" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="182" spans="2:6">
-      <c r="B182" s="3" t="s">
+      <c r="B182" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C182" s="3"/>
-      <c r="D182" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E182" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F182" s="3" t="s">
+      <c r="C182" s="2"/>
+      <c r="D182" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F182" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="183" spans="2:6">
-      <c r="B183" s="3" t="s">
+      <c r="B183" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C183" s="3"/>
-      <c r="D183" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E183" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F183" s="3" t="s">
+      <c r="C183" s="2"/>
+      <c r="D183" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F183" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="184" spans="2:6">
-      <c r="B184" s="3" t="s">
+      <c r="B184" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C184" s="3"/>
-      <c r="D184" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E184" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F184" s="3" t="s">
+      <c r="C184" s="2"/>
+      <c r="D184" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F184" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="185" spans="2:6">
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C185" s="3"/>
-      <c r="D185" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E185" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F185" s="3" t="s">
+      <c r="C185" s="2"/>
+      <c r="D185" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F185" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="186" spans="2:6">
-      <c r="B186" s="3" t="s">
+      <c r="B186" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C186" s="3"/>
-      <c r="D186" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E186" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F186" s="3" t="s">
+      <c r="C186" s="2"/>
+      <c r="D186" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F186" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="187" spans="2:6">
-      <c r="B187" s="3" t="s">
+      <c r="B187" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C187" s="3"/>
-      <c r="D187" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E187" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F187" s="3" t="s">
+      <c r="C187" s="2"/>
+      <c r="D187" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F187" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="188" spans="2:6">
-      <c r="B188" s="3" t="s">
+      <c r="B188" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C188" s="3"/>
-      <c r="D188" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E188" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F188" s="3" t="s">
+      <c r="C188" s="2"/>
+      <c r="D188" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F188" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="189" spans="2:6">
-      <c r="B189" s="3" t="s">
+      <c r="B189" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C189" s="3"/>
-      <c r="D189" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E189" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F189" s="3" t="s">
+      <c r="C189" s="2"/>
+      <c r="D189" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F189" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="190" spans="2:6">
-      <c r="B190" s="3" t="s">
+      <c r="B190" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C190" s="3"/>
-      <c r="D190" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E190" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F190" s="3" t="s">
+      <c r="C190" s="2"/>
+      <c r="D190" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F190" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="191" spans="2:6">
-      <c r="B191" s="3" t="s">
+      <c r="B191" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C191" s="3"/>
-      <c r="D191" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F191" s="3" t="s">
+      <c r="C191" s="2"/>
+      <c r="D191" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F191" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="192" spans="2:6">
-      <c r="B192" s="3" t="s">
+      <c r="B192" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C192" s="3"/>
-      <c r="D192" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E192" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F192" s="3" t="s">
+      <c r="C192" s="2"/>
+      <c r="D192" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F192" s="2" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="193" spans="2:6">
-      <c r="B193" s="3" t="s">
+      <c r="B193" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C193" s="3"/>
-      <c r="D193" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E193" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F193" s="3" t="s">
+      <c r="C193" s="2"/>
+      <c r="D193" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F193" s="2" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="194" spans="2:6">
-      <c r="B194" s="3" t="s">
+      <c r="B194" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C194" s="3"/>
-      <c r="D194" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E194" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F194" s="3" t="s">
+      <c r="C194" s="2"/>
+      <c r="D194" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F194" s="2" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="195" spans="2:6">
-      <c r="B195" s="3" t="s">
+      <c r="B195" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C195" s="3"/>
-      <c r="D195" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E195" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F195" s="3" t="s">
+      <c r="C195" s="2"/>
+      <c r="D195" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F195" s="2" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="196" spans="2:6">
-      <c r="B196" s="3" t="s">
+      <c r="B196" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C196" s="3"/>
-      <c r="D196" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F196" s="3" t="s">
+      <c r="C196" s="2"/>
+      <c r="D196" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F196" s="2" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="197" spans="2:6">
-      <c r="B197" s="3" t="s">
+      <c r="B197" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C197" s="3"/>
-      <c r="D197" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F197" s="3" t="s">
+      <c r="C197" s="2"/>
+      <c r="D197" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F197" s="2" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="198" spans="2:6">
-      <c r="B198" s="3" t="s">
+      <c r="B198" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C198" s="3"/>
-      <c r="D198" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E198" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F198" s="3" t="s">
+      <c r="C198" s="2"/>
+      <c r="D198" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F198" s="2" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="199" spans="2:6">
-      <c r="B199" s="3" t="s">
+      <c r="B199" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C199" s="3"/>
-      <c r="D199" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E199" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F199" s="3" t="s">
+      <c r="C199" s="2"/>
+      <c r="D199" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F199" s="2" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="200" spans="2:6">
-      <c r="B200" s="3" t="s">
+      <c r="B200" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C200" s="3"/>
-      <c r="D200" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E200" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F200" s="3" t="s">
+      <c r="C200" s="2"/>
+      <c r="D200" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F200" s="2" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="201" spans="2:6">
-      <c r="B201" s="3" t="s">
+      <c r="B201" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C201" s="3"/>
-      <c r="D201" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E201" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F201" s="3" t="s">
+      <c r="C201" s="2"/>
+      <c r="D201" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F201" s="2" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="202" spans="2:6">
-      <c r="B202" s="3" t="s">
+      <c r="B202" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C202" s="3"/>
-      <c r="D202" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E202" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F202" s="3" t="s">
+      <c r="C202" s="2"/>
+      <c r="D202" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F202" s="2" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="203" spans="2:6">
-      <c r="B203" s="3" t="s">
+      <c r="B203" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C203" s="3"/>
-      <c r="D203" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E203" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F203" s="3" t="s">
+      <c r="C203" s="2"/>
+      <c r="D203" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F203" s="2" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="204" spans="2:6">
-      <c r="B204" s="3" t="s">
+      <c r="B204" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C204" s="3"/>
-      <c r="D204" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E204" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F204" s="3" t="s">
+      <c r="C204" s="2"/>
+      <c r="D204" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F204" s="2" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="205" spans="2:6">
-      <c r="B205" s="3" t="s">
+      <c r="B205" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C205" s="3"/>
-      <c r="D205" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E205" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F205" s="3" t="s">
+      <c r="C205" s="2"/>
+      <c r="D205" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F205" s="2" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="206" spans="2:6">
-      <c r="B206" s="3" t="s">
+      <c r="B206" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C206" s="3"/>
-      <c r="D206" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E206" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F206" s="3" t="s">
+      <c r="C206" s="2"/>
+      <c r="D206" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F206" s="2" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="207" spans="2:6">
-      <c r="B207" s="3" t="s">
+      <c r="B207" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C207" s="3"/>
-      <c r="D207" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E207" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F207" s="3" t="s">
+      <c r="C207" s="2"/>
+      <c r="D207" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F207" s="2" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="208" spans="2:6">
-      <c r="B208" s="3" t="s">
+      <c r="B208" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C208" s="3"/>
-      <c r="D208" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E208" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F208" s="3" t="s">
+      <c r="C208" s="2"/>
+      <c r="D208" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F208" s="2" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="209" spans="2:6">
-      <c r="B209" s="3" t="s">
+      <c r="B209" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C209" s="3"/>
-      <c r="D209" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E209" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F209" s="3" t="s">
+      <c r="C209" s="2"/>
+      <c r="D209" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F209" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="210" spans="2:6">
-      <c r="B210" s="3" t="s">
+      <c r="B210" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C210" s="3"/>
-      <c r="D210" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E210" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F210" s="3" t="s">
+      <c r="C210" s="2"/>
+      <c r="D210" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F210" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="211" spans="2:6">
-      <c r="B211" s="3" t="s">
+      <c r="B211" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C211" s="3"/>
-      <c r="D211" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F211" s="3" t="s">
+      <c r="C211" s="2"/>
+      <c r="D211" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F211" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="212" spans="2:6">
-      <c r="B212" s="3" t="s">
+      <c r="B212" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C212" s="3"/>
-      <c r="D212" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E212" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F212" s="3" t="s">
+      <c r="C212" s="2"/>
+      <c r="D212" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F212" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="213" spans="2:6">
-      <c r="B213" s="3" t="s">
+      <c r="B213" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C213" s="3"/>
-      <c r="D213" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E213" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F213" s="3" t="s">
+      <c r="C213" s="2"/>
+      <c r="D213" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F213" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="214" spans="2:6">
-      <c r="B214" s="3" t="s">
+      <c r="B214" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C214" s="3"/>
-      <c r="D214" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E214" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F214" s="3" t="s">
+      <c r="C214" s="2"/>
+      <c r="D214" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F214" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="215" spans="2:6">
-      <c r="B215" s="3" t="s">
+      <c r="B215" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C215" s="3"/>
-      <c r="D215" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E215" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F215" s="3" t="s">
+      <c r="C215" s="2"/>
+      <c r="D215" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F215" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="216" spans="2:6">
-      <c r="B216" s="3" t="s">
+      <c r="B216" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C216" s="3"/>
-      <c r="D216" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E216" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F216" s="3" t="s">
+      <c r="C216" s="2"/>
+      <c r="D216" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F216" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="217" spans="2:6">
-      <c r="B217" s="3" t="s">
+      <c r="B217" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C217" s="3"/>
-      <c r="D217" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E217" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F217" s="3" t="s">
+      <c r="C217" s="2"/>
+      <c r="D217" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F217" s="2" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="218" spans="2:6">
-      <c r="B218" s="3" t="s">
+      <c r="B218" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C218" s="3"/>
-      <c r="D218" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E218" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F218" s="3" t="s">
+      <c r="C218" s="2"/>
+      <c r="D218" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F218" s="2" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="219" spans="2:6">
-      <c r="B219" s="3" t="s">
+      <c r="B219" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C219" s="3"/>
-      <c r="D219" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E219" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F219" s="3" t="s">
+      <c r="C219" s="2"/>
+      <c r="D219" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F219" s="2" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="220" spans="2:6">
-      <c r="B220" s="3" t="s">
+      <c r="B220" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C220" s="3"/>
-      <c r="D220" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E220" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F220" s="3" t="s">
+      <c r="C220" s="2"/>
+      <c r="D220" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F220" s="2" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="221" spans="2:6">
-      <c r="B221" s="3" t="s">
+      <c r="B221" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C221" s="3"/>
-      <c r="D221" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E221" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F221" s="3" t="s">
+      <c r="C221" s="2"/>
+      <c r="D221" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="222" spans="2:6">
-      <c r="B222" s="3" t="s">
+      <c r="B222" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C222" s="3"/>
-      <c r="D222" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E222" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F222" s="3" t="s">
+      <c r="C222" s="2"/>
+      <c r="D222" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F222" s="2" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="223" spans="2:6">
-      <c r="B223" s="3" t="s">
+      <c r="B223" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="C223" s="3"/>
-      <c r="D223" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E223" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F223" s="3" t="s">
+      <c r="C223" s="2"/>
+      <c r="D223" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F223" s="2" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="224" spans="2:6">
-      <c r="B224" s="3" t="s">
+      <c r="B224" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C224" s="3"/>
-      <c r="D224" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E224" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F224" s="3" t="s">
+      <c r="C224" s="2"/>
+      <c r="D224" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="225" spans="2:6">
-      <c r="B225" s="3" t="s">
+      <c r="B225" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C225" s="3"/>
-      <c r="D225" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E225" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F225" s="3" t="s">
+      <c r="C225" s="2"/>
+      <c r="D225" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F225" s="2" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="226" spans="2:6">
-      <c r="B226" s="3" t="s">
+      <c r="B226" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C226" s="3"/>
-      <c r="D226" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E226" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F226" s="3" t="s">
+      <c r="C226" s="2"/>
+      <c r="D226" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F226" s="2" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="227" spans="2:6">
-      <c r="B227" s="3" t="s">
+      <c r="B227" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C227" s="3"/>
-      <c r="D227" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E227" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F227" s="3" t="s">
+      <c r="C227" s="2"/>
+      <c r="D227" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F227" s="2" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="228" spans="2:6">
-      <c r="B228" s="3" t="s">
+      <c r="B228" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C228" s="3"/>
-      <c r="D228" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F228" s="3" t="s">
+      <c r="C228" s="2"/>
+      <c r="D228" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F228" s="2" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="229" spans="2:6">
-      <c r="B229" s="3" t="s">
+      <c r="B229" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C229" s="3"/>
-      <c r="D229" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E229" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F229" s="3" t="s">
+      <c r="C229" s="2"/>
+      <c r="D229" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F229" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="230" spans="2:6">
-      <c r="B230" s="3" t="s">
+      <c r="B230" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C230" s="3"/>
-      <c r="D230" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E230" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F230" s="3" t="s">
+      <c r="C230" s="2"/>
+      <c r="D230" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F230" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="231" spans="2:6">
-      <c r="B231" s="3" t="s">
+      <c r="B231" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="C231" s="3"/>
-      <c r="D231" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E231" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F231" s="3" t="s">
+      <c r="C231" s="2"/>
+      <c r="D231" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F231" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="232" spans="2:6">
-      <c r="B232" s="3" t="s">
+      <c r="B232" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C232" s="3"/>
-      <c r="D232" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E232" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F232" s="3" t="s">
+      <c r="C232" s="2"/>
+      <c r="D232" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F232" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="233" spans="2:6">
-      <c r="B233" s="3" t="s">
+      <c r="B233" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C233" s="3"/>
-      <c r="D233" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E233" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F233" s="3" t="s">
+      <c r="C233" s="2"/>
+      <c r="D233" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F233" s="2" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="234" spans="2:6">
-      <c r="B234" s="3" t="s">
+      <c r="B234" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C234" s="3"/>
-      <c r="D234" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E234" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F234" s="3" t="s">
+      <c r="C234" s="2"/>
+      <c r="D234" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F234" s="2" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="235" spans="2:6">
-      <c r="B235" s="3" t="s">
+      <c r="B235" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="C235" s="3"/>
-      <c r="D235" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E235" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F235" s="3" t="s">
+      <c r="C235" s="2"/>
+      <c r="D235" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F235" s="2" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="236" spans="2:6">
-      <c r="B236" s="3" t="s">
+      <c r="B236" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="C236" s="3"/>
-      <c r="D236" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E236" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F236" s="3" t="s">
+      <c r="C236" s="2"/>
+      <c r="D236" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F236" s="2" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="237" spans="2:6">
-      <c r="B237" s="3" t="s">
+      <c r="B237" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C237" s="3"/>
-      <c r="D237" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E237" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F237" s="3" t="s">
+      <c r="C237" s="2"/>
+      <c r="D237" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F237" s="2" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="238" spans="2:6">
-      <c r="B238" s="3" t="s">
+      <c r="B238" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C238" s="3"/>
-      <c r="D238" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E238" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F238" s="3" t="s">
+      <c r="C238" s="2"/>
+      <c r="D238" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F238" s="2" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="239" spans="2:6">
-      <c r="B239" s="3" t="s">
+      <c r="B239" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C239" s="3"/>
-      <c r="D239" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E239" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F239" s="3" t="s">
+      <c r="C239" s="2"/>
+      <c r="D239" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F239" s="2" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="240" spans="2:6">
-      <c r="B240" s="3" t="s">
+      <c r="B240" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C240" s="3"/>
-      <c r="D240" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E240" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F240" s="3" t="s">
+      <c r="C240" s="2"/>
+      <c r="D240" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F240" s="2" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="241" spans="2:6">
-      <c r="B241" s="3" t="s">
+      <c r="B241" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="C241" s="3"/>
-      <c r="D241" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E241" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F241" s="3" t="s">
+      <c r="C241" s="2"/>
+      <c r="D241" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F241" s="2" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="242" spans="2:6">
-      <c r="B242" s="3" t="s">
+      <c r="B242" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C242" s="3"/>
-      <c r="D242" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E242" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F242" s="3" t="s">
+      <c r="C242" s="2"/>
+      <c r="D242" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F242" s="2" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="243" spans="2:6">
-      <c r="B243" s="3" t="s">
+      <c r="B243" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C243" s="3"/>
-      <c r="D243" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E243" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F243" s="3" t="s">
+      <c r="C243" s="2"/>
+      <c r="D243" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F243" s="2" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="244" spans="2:6">
-      <c r="B244" s="3" t="s">
+      <c r="B244" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="C244" s="3"/>
-      <c r="D244" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E244" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F244" s="3" t="s">
+      <c r="C244" s="2"/>
+      <c r="D244" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F244" s="2" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="245" spans="2:6">
-      <c r="B245" s="3" t="s">
+      <c r="B245" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C245" s="3"/>
-      <c r="D245" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E245" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F245" s="3" t="s">
+      <c r="C245" s="2"/>
+      <c r="D245" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F245" s="2" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="246" spans="2:6">
-      <c r="B246" s="3" t="s">
+      <c r="B246" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C246" s="3"/>
-      <c r="D246" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E246" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F246" s="3" t="s">
+      <c r="C246" s="2"/>
+      <c r="D246" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F246" s="2" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="247" spans="2:6">
-      <c r="B247" s="3" t="s">
+      <c r="B247" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="C247" s="3"/>
-      <c r="D247" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E247" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F247" s="3" t="s">
+      <c r="C247" s="2"/>
+      <c r="D247" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F247" s="2" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="248" spans="2:6">
-      <c r="B248" s="3" t="s">
+      <c r="B248" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C248" s="3"/>
-      <c r="D248" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E248" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F248" s="3" t="s">
+      <c r="C248" s="2"/>
+      <c r="D248" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F248" s="2" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="249" spans="2:6">
-      <c r="B249" s="3" t="s">
+      <c r="B249" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="C249" s="3"/>
-      <c r="D249" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E249" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F249" s="3" t="s">
+      <c r="C249" s="2"/>
+      <c r="D249" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F249" s="2" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="250" spans="2:6">
-      <c r="B250" s="3" t="s">
+      <c r="B250" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C250" s="3"/>
-      <c r="D250" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E250" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F250" s="3" t="s">
+      <c r="C250" s="2"/>
+      <c r="D250" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F250" s="2" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="251" spans="2:6">
-      <c r="B251" s="3" t="s">
+      <c r="B251" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C251" s="3"/>
-      <c r="D251" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E251" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F251" s="3" t="s">
+      <c r="C251" s="2"/>
+      <c r="D251" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F251" s="2" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="252" spans="2:6">
-      <c r="B252" s="3" t="s">
+      <c r="B252" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C252" s="3"/>
-      <c r="D252" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E252" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F252" s="3" t="s">
+      <c r="C252" s="2"/>
+      <c r="D252" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F252" s="2" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="253" spans="2:6">
-      <c r="B253" s="3" t="s">
+      <c r="B253" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C253" s="3"/>
-      <c r="D253" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E253" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F253" s="3" t="s">
+      <c r="C253" s="2"/>
+      <c r="D253" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F253" s="2" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="254" spans="2:6">
-      <c r="B254" s="3" t="s">
+      <c r="B254" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C254" s="3"/>
-      <c r="D254" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E254" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F254" s="3" t="s">
+      <c r="C254" s="2"/>
+      <c r="D254" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F254" s="2" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="255" spans="2:6">
-      <c r="B255" s="3" t="s">
+      <c r="B255" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C255" s="3"/>
-      <c r="D255" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E255" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F255" s="3" t="s">
+      <c r="C255" s="2"/>
+      <c r="D255" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F255" s="2" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="256" spans="2:6">
-      <c r="B256" s="3" t="s">
+      <c r="B256" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C256" s="3"/>
-      <c r="D256" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E256" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F256" s="3" t="s">
+      <c r="C256" s="2"/>
+      <c r="D256" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F256" s="2" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="257" spans="2:6">
-      <c r="B257" s="3" t="s">
+      <c r="B257" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C257" s="3"/>
-      <c r="D257" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E257" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F257" s="3" t="s">
+      <c r="C257" s="2"/>
+      <c r="D257" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F257" s="2" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="258" spans="2:6">
-      <c r="B258" s="3" t="s">
+      <c r="B258" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C258" s="3"/>
-      <c r="D258" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E258" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F258" s="3" t="s">
+      <c r="C258" s="2"/>
+      <c r="D258" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F258" s="2" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="259" spans="2:6">
-      <c r="B259" s="3" t="s">
+      <c r="B259" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C259" s="3"/>
-      <c r="D259" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E259" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F259" s="3" t="s">
+      <c r="C259" s="2"/>
+      <c r="D259" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F259" s="2" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="260" spans="2:6">
-      <c r="B260" s="3" t="s">
+      <c r="B260" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="C260" s="3"/>
-      <c r="D260" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E260" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F260" s="3" t="s">
+      <c r="C260" s="2"/>
+      <c r="D260" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F260" s="2" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="261" spans="2:6">
-      <c r="B261" s="3" t="s">
+      <c r="B261" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="C261" s="3"/>
-      <c r="D261" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E261" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F261" s="3" t="s">
+      <c r="C261" s="2"/>
+      <c r="D261" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F261" s="2" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="262" spans="2:6">
-      <c r="B262" s="3" t="s">
+      <c r="B262" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C262" s="3"/>
-      <c r="D262" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E262" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F262" s="3" t="s">
+      <c r="C262" s="2"/>
+      <c r="D262" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F262" s="2" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="263" spans="2:6">
-      <c r="B263" s="3" t="s">
+      <c r="B263" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C263" s="3"/>
-      <c r="D263" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E263" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F263" s="3" t="s">
+      <c r="C263" s="2"/>
+      <c r="D263" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F263" s="2" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="264" spans="2:6">
-      <c r="B264" s="3" t="s">
+      <c r="B264" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C264" s="3"/>
-      <c r="D264" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E264" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F264" s="3" t="s">
+      <c r="C264" s="2"/>
+      <c r="D264" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F264" s="2" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="265" spans="2:6">
-      <c r="B265" s="3" t="s">
+      <c r="B265" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C265" s="3"/>
-      <c r="D265" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E265" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F265" s="3" t="s">
+      <c r="C265" s="2"/>
+      <c r="D265" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F265" s="2" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="266" spans="2:6">
-      <c r="B266" s="3" t="s">
+      <c r="B266" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C266" s="3"/>
-      <c r="D266" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E266" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F266" s="3" t="s">
+      <c r="C266" s="2"/>
+      <c r="D266" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F266" s="2" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="267" spans="2:6">
-      <c r="B267" s="3" t="s">
+      <c r="B267" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C267" s="3"/>
-      <c r="D267" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E267" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F267" s="3" t="s">
+      <c r="C267" s="2"/>
+      <c r="D267" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F267" s="2" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="268" spans="2:6">
-      <c r="B268" s="3" t="s">
+      <c r="B268" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="C268" s="3"/>
-      <c r="D268" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E268" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F268" s="3" t="s">
+      <c r="C268" s="2"/>
+      <c r="D268" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F268" s="2" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="269" spans="2:6">
-      <c r="B269" s="3" t="s">
+      <c r="B269" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C269" s="3"/>
-      <c r="D269" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E269" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F269" s="3" t="s">
+      <c r="C269" s="2"/>
+      <c r="D269" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F269" s="2" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="270" spans="2:6">
-      <c r="B270" s="3" t="s">
+      <c r="B270" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C270" s="3"/>
-      <c r="D270" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E270" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F270" s="3" t="s">
+      <c r="C270" s="2"/>
+      <c r="D270" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F270" s="2" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="271" spans="2:6">
-      <c r="B271" s="3" t="s">
+      <c r="B271" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="C271" s="3"/>
-      <c r="D271" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E271" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F271" s="3" t="s">
+      <c r="C271" s="2"/>
+      <c r="D271" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F271" s="2" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="272" spans="2:6">
-      <c r="B272" s="3" t="s">
+      <c r="B272" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C272" s="3"/>
-      <c r="D272" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E272" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F272" s="3" t="s">
+      <c r="C272" s="2"/>
+      <c r="D272" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F272" s="2" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="273" spans="2:6">
-      <c r="B273" s="3" t="s">
+      <c r="B273" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="C273" s="3"/>
-      <c r="D273" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E273" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F273" s="3" t="s">
+      <c r="C273" s="2"/>
+      <c r="D273" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F273" s="2" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="274" spans="2:6">
-      <c r="B274" s="3" t="s">
+      <c r="B274" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="C274" s="3"/>
-      <c r="D274" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E274" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F274" s="3" t="s">
+      <c r="C274" s="2"/>
+      <c r="D274" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F274" s="2" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="275" spans="2:6">
-      <c r="B275" s="3" t="s">
+      <c r="B275" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="C275" s="3"/>
-      <c r="D275" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E275" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F275" s="3" t="s">
+      <c r="C275" s="2"/>
+      <c r="D275" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F275" s="2" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="276" spans="2:6">
-      <c r="B276" s="3" t="s">
+      <c r="B276" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="C276" s="3"/>
-      <c r="D276" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E276" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F276" s="3" t="s">
+      <c r="C276" s="2"/>
+      <c r="D276" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F276" s="2" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="277" spans="2:6">
-      <c r="B277" s="3" t="s">
+      <c r="B277" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C277" s="3"/>
-      <c r="D277" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E277" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F277" s="3" t="s">
+      <c r="C277" s="2"/>
+      <c r="D277" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F277" s="2" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="278" spans="2:6">
-      <c r="B278" s="3" t="s">
+      <c r="B278" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C278" s="3"/>
-      <c r="D278" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E278" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F278" s="3" t="s">
+      <c r="C278" s="2"/>
+      <c r="D278" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F278" s="2" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="279" spans="2:6">
-      <c r="B279" s="3" t="s">
+      <c r="B279" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="C279" s="3"/>
-      <c r="D279" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E279" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F279" s="3" t="s">
+      <c r="C279" s="2"/>
+      <c r="D279" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F279" s="2" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="280" spans="2:6">
-      <c r="B280" s="3" t="s">
+      <c r="B280" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C280" s="3"/>
-      <c r="D280" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E280" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F280" s="3" t="s">
+      <c r="C280" s="2"/>
+      <c r="D280" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F280" s="2" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="281" spans="2:6">
-      <c r="B281" s="3" t="s">
+      <c r="B281" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="C281" s="3"/>
-      <c r="D281" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E281" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F281" s="3" t="s">
+      <c r="C281" s="2"/>
+      <c r="D281" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F281" s="2" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="282" spans="2:6">
-      <c r="B282" s="3" t="s">
+      <c r="B282" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="C282" s="3"/>
-      <c r="D282" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E282" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F282" s="3" t="s">
+      <c r="C282" s="2"/>
+      <c r="D282" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F282" s="2" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="283" spans="2:6">
-      <c r="B283" s="3" t="s">
+      <c r="B283" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C283" s="3"/>
-      <c r="D283" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E283" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F283" s="3" t="s">
+      <c r="C283" s="2"/>
+      <c r="D283" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F283" s="2" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="284" spans="2:6">
-      <c r="B284" s="3" t="s">
+      <c r="B284" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C284" s="3"/>
-      <c r="D284" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E284" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F284" s="3" t="s">
+      <c r="C284" s="2"/>
+      <c r="D284" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F284" s="2" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="285" spans="2:6">
-      <c r="B285" s="3" t="s">
+      <c r="B285" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C285" s="3"/>
-      <c r="D285" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E285" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F285" s="3" t="s">
+      <c r="C285" s="2"/>
+      <c r="D285" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F285" s="2" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="286" spans="2:6">
-      <c r="B286" s="3" t="s">
+      <c r="B286" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="C286" s="3"/>
-      <c r="D286" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E286" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F286" s="3" t="s">
+      <c r="C286" s="2"/>
+      <c r="D286" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F286" s="2" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="287" spans="2:6">
-      <c r="B287" s="3" t="s">
+      <c r="B287" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C287" s="3"/>
-      <c r="D287" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E287" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F287" s="3" t="s">
+      <c r="C287" s="2"/>
+      <c r="D287" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F287" s="2" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="288" spans="2:6">
-      <c r="B288" s="3" t="s">
+      <c r="B288" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C288" s="3"/>
-      <c r="D288" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E288" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F288" s="3" t="s">
+      <c r="C288" s="2"/>
+      <c r="D288" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F288" s="2" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="289" spans="2:6">
-      <c r="B289" s="3" t="s">
+      <c r="B289" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C289" s="3"/>
-      <c r="D289" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E289" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F289" s="3" t="s">
+      <c r="C289" s="2"/>
+      <c r="D289" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F289" s="2" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="290" spans="2:6">
-      <c r="B290" s="3" t="s">
+      <c r="B290" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C290" s="3"/>
-      <c r="D290" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E290" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F290" s="3" t="s">
+      <c r="C290" s="2"/>
+      <c r="D290" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F290" s="2" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="291" spans="2:6">
-      <c r="B291" s="3" t="s">
+      <c r="B291" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="C291" s="3"/>
-      <c r="D291" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E291" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F291" s="3" t="s">
+      <c r="C291" s="2"/>
+      <c r="D291" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F291" s="2" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="292" spans="2:6">
-      <c r="B292" s="3" t="s">
+      <c r="B292" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C292" s="3"/>
-      <c r="D292" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E292" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F292" s="3" t="s">
+      <c r="C292" s="2"/>
+      <c r="D292" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F292" s="2" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="293" spans="2:6">
-      <c r="B293" s="3" t="s">
+      <c r="B293" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C293" s="3"/>
-      <c r="D293" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E293" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F293" s="3" t="s">
+      <c r="C293" s="2"/>
+      <c r="D293" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F293" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="294" spans="2:6">
-      <c r="B294" s="3" t="s">
+      <c r="B294" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C294" s="3"/>
-      <c r="D294" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E294" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F294" s="3" t="s">
+      <c r="C294" s="2"/>
+      <c r="D294" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E294" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F294" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="295" spans="2:6">
-      <c r="B295" s="3" t="s">
+      <c r="B295" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="C295" s="3"/>
-      <c r="D295" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E295" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F295" s="3" t="s">
+      <c r="C295" s="2"/>
+      <c r="D295" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E295" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F295" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="296" spans="2:6">
-      <c r="B296" s="3" t="s">
+      <c r="B296" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C296" s="3"/>
-      <c r="D296" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E296" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F296" s="3" t="s">
+      <c r="C296" s="2"/>
+      <c r="D296" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F296" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="297" spans="2:6">
-      <c r="B297" s="3" t="s">
+      <c r="B297" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="C297" s="3"/>
-      <c r="D297" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E297" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F297" s="3" t="s">
+      <c r="C297" s="2"/>
+      <c r="D297" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E297" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F297" s="2" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="298" spans="2:6">
-      <c r="B298" s="3" t="s">
+      <c r="B298" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C298" s="3"/>
-      <c r="D298" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E298" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F298" s="3" t="s">
+      <c r="C298" s="2"/>
+      <c r="D298" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F298" s="2" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="299" spans="2:6">
-      <c r="B299" s="3" t="s">
+      <c r="B299" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="C299" s="3"/>
-      <c r="D299" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E299" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F299" s="3" t="s">
+      <c r="C299" s="2"/>
+      <c r="D299" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E299" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F299" s="2" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="300" spans="2:6">
-      <c r="B300" s="3" t="s">
+      <c r="B300" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C300" s="3"/>
-      <c r="D300" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E300" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F300" s="3" t="s">
+      <c r="C300" s="2"/>
+      <c r="D300" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E300" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F300" s="2" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="301" spans="2:6">
-      <c r="B301" s="3" t="s">
+      <c r="B301" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C301" s="3"/>
-      <c r="D301" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E301" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F301" s="3" t="s">
+      <c r="C301" s="2"/>
+      <c r="D301" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E301" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F301" s="2" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="302" spans="2:6">
-      <c r="B302" s="3" t="s">
+      <c r="B302" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C302" s="3"/>
-      <c r="D302" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E302" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F302" s="3" t="s">
+      <c r="C302" s="2"/>
+      <c r="D302" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E302" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F302" s="2" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="303" spans="2:6">
-      <c r="B303" s="3" t="s">
+      <c r="B303" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C303" s="3"/>
-      <c r="D303" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E303" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F303" s="3" t="s">
+      <c r="C303" s="2"/>
+      <c r="D303" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F303" s="2" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="304" spans="2:6">
-      <c r="B304" s="3" t="s">
+      <c r="B304" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="C304" s="3"/>
-      <c r="D304" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E304" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F304" s="3" t="s">
+      <c r="C304" s="2"/>
+      <c r="D304" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E304" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F304" s="2" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="305" spans="2:6">
-      <c r="B305" s="3" t="s">
+      <c r="B305" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C305" s="3"/>
-      <c r="D305" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E305" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F305" s="3" t="s">
+      <c r="C305" s="2"/>
+      <c r="D305" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E305" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F305" s="2" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="306" spans="2:6">
-      <c r="B306" s="3" t="s">
+      <c r="B306" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C306" s="3"/>
-      <c r="D306" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E306" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F306" s="3" t="s">
+      <c r="C306" s="2"/>
+      <c r="D306" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E306" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F306" s="2" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="307" spans="2:6">
-      <c r="B307" s="3" t="s">
+      <c r="B307" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C307" s="3"/>
-      <c r="D307" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E307" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F307" s="3" t="s">
+      <c r="C307" s="2"/>
+      <c r="D307" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E307" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F307" s="2" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="308" spans="2:6">
-      <c r="B308" s="3" t="s">
+      <c r="B308" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="C308" s="3"/>
-      <c r="D308" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E308" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F308" s="3" t="s">
+      <c r="C308" s="2"/>
+      <c r="D308" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E308" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F308" s="2" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="309" spans="2:6">
-      <c r="B309" s="3" t="s">
+      <c r="B309" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="C309" s="3"/>
-      <c r="D309" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E309" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F309" s="3" t="s">
+      <c r="C309" s="2"/>
+      <c r="D309" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E309" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F309" s="2" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="310" spans="2:6">
-      <c r="B310" s="3" t="s">
+      <c r="B310" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="C310" s="3"/>
-      <c r="D310" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E310" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F310" s="3" t="s">
+      <c r="C310" s="2"/>
+      <c r="D310" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E310" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F310" s="2" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="311" spans="2:6">
-      <c r="B311" s="3" t="s">
+      <c r="B311" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="C311" s="3"/>
-      <c r="D311" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E311" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F311" s="3" t="s">
+      <c r="C311" s="2"/>
+      <c r="D311" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E311" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F311" s="2" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="312" spans="2:6">
-      <c r="B312" s="3" t="s">
+      <c r="B312" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="C312" s="3"/>
-      <c r="D312" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E312" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F312" s="3" t="s">
+      <c r="C312" s="2"/>
+      <c r="D312" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F312" s="2" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="313" spans="2:6">
-      <c r="B313" s="3" t="s">
+      <c r="B313" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="C313" s="3"/>
-      <c r="D313" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E313" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F313" s="3" t="s">
+      <c r="C313" s="2"/>
+      <c r="D313" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E313" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F313" s="2" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="314" spans="2:6">
-      <c r="B314" s="3" t="s">
+      <c r="B314" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C314" s="3"/>
-      <c r="D314" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E314" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F314" s="3" t="s">
+      <c r="C314" s="2"/>
+      <c r="D314" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E314" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F314" s="2" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="315" spans="2:6">
-      <c r="B315" s="3" t="s">
+      <c r="B315" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="C315" s="3"/>
-      <c r="D315" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E315" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F315" s="3" t="s">
+      <c r="C315" s="2"/>
+      <c r="D315" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E315" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F315" s="2" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="316" spans="2:6">
-      <c r="B316" s="3" t="s">
+      <c r="B316" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="C316" s="3"/>
-      <c r="D316" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E316" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F316" s="3" t="s">
+      <c r="C316" s="2"/>
+      <c r="D316" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F316" s="2" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="317" spans="2:6">
-      <c r="B317" s="3" t="s">
+      <c r="B317" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C317" s="3"/>
-      <c r="D317" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E317" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F317" s="3" t="s">
+      <c r="C317" s="2"/>
+      <c r="D317" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E317" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F317" s="2" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="318" spans="2:6">
-      <c r="B318" s="3" t="s">
+      <c r="B318" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C318" s="3"/>
-      <c r="D318" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E318" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F318" s="3" t="s">
+      <c r="C318" s="2"/>
+      <c r="D318" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F318" s="2" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="319" spans="2:6">
-      <c r="B319" s="3" t="s">
+      <c r="B319" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="C319" s="3"/>
-      <c r="D319" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E319" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F319" s="3" t="s">
+      <c r="C319" s="2"/>
+      <c r="D319" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F319" s="2" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="320" spans="2:6">
-      <c r="B320" s="3" t="s">
+      <c r="B320" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C320" s="3"/>
-      <c r="D320" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E320" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F320" s="3" t="s">
+      <c r="C320" s="2"/>
+      <c r="D320" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F320" s="2" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="321" spans="2:6">
-      <c r="B321" s="3" t="s">
+      <c r="B321" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C321" s="3"/>
-      <c r="D321" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E321" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F321" s="3" t="s">
+      <c r="C321" s="2"/>
+      <c r="D321" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F321" s="2" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="322" spans="2:6">
-      <c r="B322" s="3" t="s">
+      <c r="B322" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C322" s="3"/>
-      <c r="D322" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E322" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F322" s="3" t="s">
+      <c r="C322" s="2"/>
+      <c r="D322" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F322" s="2" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="323" spans="2:6">
-      <c r="B323" s="3" t="s">
+      <c r="B323" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="C323" s="3"/>
-      <c r="D323" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E323" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F323" s="3" t="s">
+      <c r="C323" s="2"/>
+      <c r="D323" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E323" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F323" s="2" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="324" spans="2:6">
-      <c r="B324" s="3" t="s">
+      <c r="B324" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="C324" s="3"/>
-      <c r="D324" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E324" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F324" s="3" t="s">
+      <c r="C324" s="2"/>
+      <c r="D324" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E324" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F324" s="2" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="325" spans="2:6">
-      <c r="B325" s="3" t="s">
+      <c r="B325" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="C325" s="3"/>
-      <c r="D325" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E325" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F325" s="3" t="s">
+      <c r="C325" s="2"/>
+      <c r="D325" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E325" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F325" s="2" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="326" spans="2:6">
-      <c r="B326" s="3" t="s">
+      <c r="B326" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C326" s="3"/>
-      <c r="D326" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E326" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F326" s="3" t="s">
+      <c r="C326" s="2"/>
+      <c r="D326" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F326" s="2" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="327" spans="2:6">
-      <c r="B327" s="3" t="s">
+      <c r="B327" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C327" s="3"/>
-      <c r="D327" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E327" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F327" s="3" t="s">
+      <c r="C327" s="2"/>
+      <c r="D327" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E327" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F327" s="2" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="328" spans="2:6">
-      <c r="B328" s="3" t="s">
+      <c r="B328" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="C328" s="3"/>
-      <c r="D328" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E328" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F328" s="3" t="s">
+      <c r="C328" s="2"/>
+      <c r="D328" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F328" s="2" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="329" spans="2:6">
-      <c r="B329" s="3" t="s">
+      <c r="B329" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="C329" s="3"/>
-      <c r="D329" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E329" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F329" s="3" t="s">
+      <c r="C329" s="2"/>
+      <c r="D329" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E329" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F329" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="330" spans="2:6">
-      <c r="B330" s="3" t="s">
+      <c r="B330" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="C330" s="3"/>
-      <c r="D330" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E330" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F330" s="3" t="s">
+      <c r="C330" s="2"/>
+      <c r="D330" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E330" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F330" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="331" spans="2:6">
-      <c r="B331" s="3" t="s">
+      <c r="B331" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C331" s="3"/>
-      <c r="D331" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E331" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F331" s="3" t="s">
+      <c r="C331" s="2"/>
+      <c r="D331" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E331" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F331" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="332" spans="2:6">
-      <c r="B332" s="3" t="s">
+      <c r="B332" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="C332" s="3"/>
-      <c r="D332" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E332" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F332" s="3" t="s">
+      <c r="C332" s="2"/>
+      <c r="D332" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E332" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F332" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="333" spans="2:6">
-      <c r="B333" s="3" t="s">
+      <c r="B333" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="C333" s="3"/>
-      <c r="D333" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E333" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F333" s="3" t="s">
+      <c r="C333" s="2"/>
+      <c r="D333" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F333" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="334" spans="2:6">
-      <c r="B334" s="3" t="s">
+      <c r="B334" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="C334" s="3"/>
-      <c r="D334" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E334" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F334" s="3" t="s">
+      <c r="C334" s="2"/>
+      <c r="D334" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E334" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F334" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="335" spans="2:6">
-      <c r="B335" s="3" t="s">
+      <c r="B335" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C335" s="3"/>
-      <c r="D335" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E335" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F335" s="3" t="s">
+      <c r="C335" s="2"/>
+      <c r="D335" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E335" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F335" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="336" spans="2:6">
-      <c r="B336" s="3" t="s">
+      <c r="B336" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="C336" s="3"/>
-      <c r="D336" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E336" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F336" s="3" t="s">
+      <c r="C336" s="2"/>
+      <c r="D336" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E336" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F336" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="337" spans="2:6">
-      <c r="B337" s="3" t="s">
+      <c r="B337" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="C337" s="3"/>
-      <c r="D337" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E337" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F337" s="3" t="s">
+      <c r="C337" s="2"/>
+      <c r="D337" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E337" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F337" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="338" spans="2:6">
-      <c r="B338" s="3" t="s">
+      <c r="B338" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="C338" s="3"/>
-      <c r="D338" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E338" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F338" s="3" t="s">
+      <c r="C338" s="2"/>
+      <c r="D338" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E338" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F338" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="339" spans="2:6">
-      <c r="B339" s="3" t="s">
+      <c r="B339" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="C339" s="3"/>
-      <c r="D339" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E339" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F339" s="3" t="s">
+      <c r="C339" s="2"/>
+      <c r="D339" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F339" s="2" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="340" spans="2:6">
-      <c r="B340" s="3" t="s">
+      <c r="B340" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="C340" s="3"/>
-      <c r="D340" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E340" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F340" s="3" t="s">
+      <c r="C340" s="2"/>
+      <c r="D340" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E340" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F340" s="2" t="s">
         <v>433</v>
       </c>
     </row>
+    <row r="341" spans="2:6">
+      <c r="B341" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C341" s="2"/>
+      <c r="D341" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E341" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F341" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="342" spans="2:6">
+      <c r="B342" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C342" s="2"/>
+      <c r="D342" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E342" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F342" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="343" spans="2:6">
+      <c r="B343" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C343" s="2"/>
+      <c r="D343" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E343" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F343" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="344" spans="2:6">
+      <c r="B344" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C344" s="2"/>
+      <c r="D344" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E344" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F344" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="345" spans="2:6">
+      <c r="B345" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C345" s="2"/>
+      <c r="D345" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F345" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="346" spans="2:6">
+      <c r="B346" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C346" s="2"/>
+      <c r="D346" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E346" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F346" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="347" spans="2:6">
+      <c r="B347" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C347" s="2"/>
+      <c r="D347" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E347" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F347" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="348" spans="2:6">
+      <c r="B348" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C348" s="2"/>
+      <c r="D348" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E348" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F348" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="349" spans="2:6">
+      <c r="B349" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C349" s="2"/>
+      <c r="D349" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E349" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F349" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="350" spans="2:6">
+      <c r="B350" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C350" s="2"/>
+      <c r="D350" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E350" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F350" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="351" spans="2:6">
+      <c r="B351" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C351" s="2"/>
+      <c r="D351" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E351" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F351" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="352" spans="2:6">
+      <c r="B352" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C352" s="2"/>
+      <c r="D352" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E352" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F352" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="353" spans="2:6">
+      <c r="B353" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C353" s="2"/>
+      <c r="D353" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E353" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F353" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="354" spans="2:6">
+      <c r="B354" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C354" s="2"/>
+      <c r="D354" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E354" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F354" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="355" spans="2:6">
+      <c r="B355" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C355" s="2"/>
+      <c r="D355" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E355" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F355" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
     <row r="356" spans="2:6">
-      <c r="B356" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="C356" s="3"/>
-      <c r="D356" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E356" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F356" s="3" t="s">
-        <v>446</v>
+      <c r="B356" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C356" s="2"/>
+      <c r="D356" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E356" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F356" s="2" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="357" spans="2:6">
-      <c r="B357" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="C357" s="3"/>
-      <c r="D357" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E357" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F357" s="3" t="s">
-        <v>446</v>
+      <c r="B357" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C357" s="2"/>
+      <c r="D357" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E357" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F357" s="2" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="358" spans="2:6">
-      <c r="B358" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="C358" s="3"/>
-      <c r="D358" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E358" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F358" s="3" t="s">
-        <v>446</v>
+      <c r="B358" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C358" s="2"/>
+      <c r="D358" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E358" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F358" s="2" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="359" spans="2:6">
-      <c r="B359" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="C359" s="3"/>
-      <c r="D359" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E359" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F359" s="3" t="s">
-        <v>446</v>
+      <c r="B359" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C359" s="2"/>
+      <c r="D359" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E359" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F359" s="2" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="360" spans="2:6">
-      <c r="B360" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C360" s="3"/>
-      <c r="D360" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E360" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F360" s="3" t="s">
-        <v>451</v>
+      <c r="B360" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C360" s="2"/>
+      <c r="D360" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E360" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F360" s="2" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="361" spans="2:6">
-      <c r="B361" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="C361" s="3"/>
-      <c r="D361" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E361" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F361" s="3" t="s">
-        <v>451</v>
+      <c r="B361" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C361" s="2"/>
+      <c r="D361" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E361" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F361" s="2" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="362" spans="2:6">
-      <c r="B362" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="C362" s="3"/>
-      <c r="D362" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E362" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F362" s="3" t="s">
-        <v>451</v>
+      <c r="B362" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C362" s="2"/>
+      <c r="D362" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E362" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F362" s="2" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="363" spans="2:6">
-      <c r="B363" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="C363" s="3"/>
-      <c r="D363" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E363" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F363" s="3" t="s">
-        <v>451</v>
+      <c r="B363" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C363" s="2"/>
+      <c r="D363" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E363" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F363" s="2" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="364" spans="2:6">
-      <c r="B364" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="C364" s="3"/>
-      <c r="D364" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E364" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F364" s="3" t="s">
-        <v>451</v>
+      <c r="B364" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C364" s="2"/>
+      <c r="D364" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E364" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F364" s="2" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="365" spans="2:6">
-      <c r="B365" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="C365" s="3"/>
-      <c r="D365" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E365" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F365" s="3" t="s">
-        <v>451</v>
+      <c r="B365" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C365" s="2"/>
+      <c r="D365" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E365" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F365" s="2" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="366" spans="2:6">
-      <c r="B366" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="C366" s="3"/>
-      <c r="D366" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E366" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F366" s="3" t="s">
-        <v>451</v>
+      <c r="B366" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C366" s="2"/>
+      <c r="D366" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E366" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F366" s="2" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="367" spans="2:6">
-      <c r="B367" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="C367" s="3"/>
-      <c r="D367" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E367" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F367" s="3" t="s">
-        <v>451</v>
+      <c r="B367" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C367" s="2"/>
+      <c r="D367" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E367" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F367" s="2" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="368" spans="2:6">
-      <c r="B368" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C368" s="3"/>
-      <c r="D368" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E368" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F368" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="369" spans="2:6">
-      <c r="B369" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="C369" s="3"/>
-      <c r="D369" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E369" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F369" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="370" spans="2:6">
-      <c r="B370" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="C370" s="3"/>
-      <c r="D370" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E370" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F370" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="371" spans="2:6">
-      <c r="B371" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="C371" s="3"/>
-      <c r="D371" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E371" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F371" s="3" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="388" spans="2:6">
-      <c r="B388" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="C388" s="3"/>
-      <c r="D388" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E388" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F388" s="3" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="389" spans="2:6">
-      <c r="B389" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C389" s="3"/>
-      <c r="D389" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E389" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F389" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="390" spans="2:6">
-      <c r="B390" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C390" s="3"/>
-      <c r="D390" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E390" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F390" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="391" spans="2:6">
-      <c r="B391" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C391" s="3"/>
-      <c r="D391" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E391" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F391" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="392" spans="2:6">
-      <c r="B392" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="C392" s="3"/>
-      <c r="D392" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E392" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F392" s="3" t="s">
+      <c r="B368" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C368" s="2"/>
+      <c r="D368" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E368" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F368" s="2" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="393" spans="2:6">
-      <c r="B393" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="C393" s="3"/>
-      <c r="D393" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E393" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F393" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="394" spans="2:6">
-      <c r="B394" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="C394" s="3"/>
-      <c r="D394" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E394" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F394" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="395" spans="2:6">
-      <c r="B395" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="C395" s="3"/>
-      <c r="D395" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E395" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F395" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="396" spans="2:6">
-      <c r="B396" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="C396" s="3"/>
-      <c r="D396" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E396" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F396" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="397" spans="2:6">
-      <c r="B397" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="C397" s="3"/>
-      <c r="D397" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E397" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F397" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="398" spans="2:6">
-      <c r="B398" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="C398" s="3"/>
-      <c r="D398" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E398" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F398" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="399" spans="2:6">
-      <c r="B399" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="C399" s="3"/>
-      <c r="D399" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E399" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F399" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="400" spans="2:6">
-      <c r="B400" s="3" t="s">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="22.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="22.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="45.1111111111111" customWidth="1"/>
+    <col min="4" max="5" width="14.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="181" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
         <v>478</v>
       </c>
-      <c r="C400" s="3"/>
-      <c r="D400" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E400" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F400" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="401" spans="2:6">
-      <c r="B401" s="3" t="s">
+      <c r="D2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" t="s">
         <v>479</v>
       </c>
-      <c r="C401" s="3"/>
-      <c r="D401" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E401" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F401" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="402" spans="2:6">
-      <c r="B402" s="3" t="s">
+    </row>
+    <row r="3" customFormat="1" spans="2:6">
+      <c r="B3" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="2:6">
+      <c r="B4" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="C402" s="3"/>
-      <c r="D402" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E402" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F402" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="403" spans="2:6">
-      <c r="B403" s="3" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="2:6">
+      <c r="B5" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C403" s="3"/>
-      <c r="D403" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E403" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F403" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="404" spans="2:6">
-      <c r="B404" s="3" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="2:6">
+      <c r="B6" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C404" s="3"/>
-      <c r="D404" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E404" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F404" s="3" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="2:6">
+      <c r="B7" s="2" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="405" spans="2:6">
-      <c r="B405" s="3" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="2:6">
+      <c r="B8" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="C405" s="3"/>
-      <c r="D405" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E405" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F405" s="3" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="2:6">
+      <c r="B9" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="2:6">
+      <c r="B10" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="2:6">
+      <c r="B11" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="2:6">
+      <c r="B12" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="2:6">
+      <c r="B13" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="2:6">
+      <c r="B14" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" t="s">
+        <v>495</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="30.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="33.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="11.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="12.4444444444444" customWidth="1"/>
+    <col min="6" max="6" width="82.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="2:6">
+      <c r="B3" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="2:6">
+      <c r="B4" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="2:6">
+      <c r="B5" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F5" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="2:6">
+      <c r="B6" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="2:6">
+      <c r="B7" s="2" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="406" spans="2:6">
-      <c r="B406" s="3" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="2:6">
+      <c r="B8" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="2:6">
+      <c r="B9" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="C406" s="3"/>
-      <c r="D406" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E406" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F406" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="407" spans="2:6">
-      <c r="B407" s="3" t="s">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="2:6">
+      <c r="B10" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="C407" s="3"/>
-      <c r="D407" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E407" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F407" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="408" spans="2:6">
-      <c r="B408" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="C408" s="3"/>
-      <c r="D408" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E408" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F408" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="409" spans="2:6">
-      <c r="B409" s="3" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="2:6">
+      <c r="B11" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C409" s="3"/>
-      <c r="D409" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E409" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F409" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="410" spans="2:6">
-      <c r="B410" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="C410" s="3"/>
-      <c r="D410" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E410" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F410" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="411" spans="2:6">
-      <c r="B411" s="3" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="2:6">
+      <c r="B12" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="C411" s="3"/>
-      <c r="D411" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E411" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F411" s="3" t="s">
-        <v>483</v>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F12" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="2:6">
+      <c r="B13" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F13" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="2:6">
+      <c r="B14" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" t="s">
+        <v>496</v>
       </c>
     </row>
   </sheetData>
